--- a/output/ML_Hires_Signal_2026-05-29.xlsx
+++ b/output/ML_Hires_Signal_2026-05-29.xlsx
@@ -33,7 +33,7 @@
       <sz val="10"/>
     </font>
     <font>
-      <color rgb="00276221"/>
+      <color rgb="009C6500"/>
       <sz val="10"/>
     </font>
     <font>
@@ -55,7 +55,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
@@ -593,7 +593,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Hot 🟩</t>
+          <t>Warm 🟨</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -606,52 +606,50 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Qualcomm Inc.</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>qualcomm.com</t>
+          <t>nvidia.com</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Outbound Now — High ML Signal</t>
+          <t>Monitor — Trending Up</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>GPU/inference signal; +29 new ML roles WoW</t>
+          <t>Director+ hiring; GPU/inference signal</t>
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
+        <v>20</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>2026 Intern-Machine Learning &amp;Multimedia Software Engineer</t>
+          <t>Principal Deep Learning Communication Architect</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
@@ -660,7 +658,7 @@
         </is>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>38962</v>
+        <v>130497</v>
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
@@ -676,7 +674,7 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Hot 🟩</t>
+          <t>Warm 🟨</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -689,61 +687,59 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Tesla Inc.</t>
+          <t>Oracle Corporation</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>tesla.com</t>
+          <t>oracle.com</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Outbound Now — High ML Signal</t>
+          <t>Monitor — Trending Up</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>GPU/inference signal; +21 new ML roles WoW</t>
+          <t>Director+ hiring; GPU/inference signal</t>
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer, HPC / AI Infrastructure</t>
+          <t>[Remote] Principal Applied Scientist</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>EV / Auto</t>
+          <t>Software / Cloud</t>
         </is>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>97690</v>
+        <v>52961</v>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
@@ -759,7 +755,7 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Hot 🟩</t>
+          <t>Warm 🟨</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -772,63 +768,59 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>nvidia.com</t>
+          <t>microsoft.com</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Outbound Now — High ML Signal</t>
+          <t>Monitor — Trending Up</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>Director+ hiring; GPU/inference signal; +20 new ML roles WoW</t>
+          <t>Director+ hiring; GPU/inference signal</t>
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>Principal Deep Learning Communication Architect</t>
+          <t>Principal Applied Scientist (CoreAI)</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>130497</v>
+        <v>245122</v>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
@@ -844,7 +836,7 @@
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Hot 🟩</t>
+          <t>Warm 🟨</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -852,68 +844,62 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>POD 4 Banking Payments Insurance</t>
+          <t>POD 5 Consumer Internet Software Auto</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co.</t>
+          <t>Uber Technologies</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>jpmorganchase.com</t>
+          <t>uber.com</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Outbound Now — High ML Signal</t>
+          <t>Monitor — Trending Up</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Director+ hiring; GPU/inference signal; +19 new ML roles WoW</t>
+          <t>GPU/inference signal</t>
         </is>
       </c>
       <c r="J5" s="3" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>Product Director Speech and Voice AI/ML</t>
+          <t>Senior Data Scientist - Applied AI</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>Money Center Bank</t>
+          <t>Mobility / Delivery</t>
         </is>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>177421</v>
+        <v>43970</v>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
@@ -929,7 +915,7 @@
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Hot 🟩</t>
+          <t>Warm 🟨</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -942,54 +928,50 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Citigroup Inc.</t>
+          <t>JPMorgan Chase &amp; Co.</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>citigroup.com</t>
+          <t>jpmorganchase.com</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Outbound Now — High ML Signal</t>
+          <t>Monitor — Trending Up</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>Director+ hiring; GPU/inference signal; +18 new ML roles WoW</t>
+          <t>Director+ hiring; GPU/inference signal</t>
         </is>
       </c>
       <c r="J6" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
+        <v>19</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M6" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>Lead AI Engineer, Banking Technology - Senior Vice President</t>
+          <t>Product Director Speech and Voice AI/ML</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
@@ -998,7 +980,7 @@
         </is>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>71355</v>
+        <v>177421</v>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
@@ -1014,7 +996,7 @@
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Hot 🟩</t>
+          <t>Warm 🟨</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -1022,68 +1004,60 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>POD 4 Banking Payments Insurance</t>
+          <t>POD 6 Cyber Telco Retail M&amp;E</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Mastercard Incorporated</t>
+          <t>Target Corporation</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>mastercard.com</t>
+          <t>target.com</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Outbound Now — High ML Signal</t>
+          <t>Monitor — Trending Up</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Director+ hiring; GPU/inference signal; +14 new ML roles WoW</t>
+          <t>Director+ hiring</t>
         </is>
       </c>
       <c r="J7" s="3" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="N7" s="2" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>Principal AI Engineer</t>
+          <t>Principal AI Engineer-Advanced AI</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>Payment Networks</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>28167</v>
+        <v>107412</v>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
@@ -1099,7 +1073,7 @@
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Hot 🟩</t>
+          <t>Warm 🟨</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -1107,66 +1081,64 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>POD 5 Consumer Internet Software Auto</t>
+          <t>POD 2 Healthcare &amp; Life Sciences</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
+          <t>Pfizer Inc.</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>apple.com</t>
+          <t>pfizer.com</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Outbound Now — High ML Signal</t>
+          <t>Monitor — Trending Up</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>GPU/inference signal; +13 new ML roles WoW</t>
+          <t>Director+ hiring; GPU/inference signal</t>
         </is>
       </c>
       <c r="J8" s="3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer – Edge AI &amp; On-Device Optimization</t>
+          <t>Principal Statistical Data Scientist</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>Consumer Tech</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>391035</v>
+        <v>63627</v>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
@@ -1182,7 +1154,7 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Hot 🟩</t>
+          <t>Warm 🟨</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1205,33 +1177,29 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Outbound Now — High ML Signal</t>
+          <t>Monitor — Trending Up</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>GPU/inference signal; +8 new ML roles WoW</t>
+          <t>GPU/inference signal</t>
         </is>
       </c>
       <c r="J9" s="3" t="n">
         <v>8</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr">
         <is>
@@ -1265,7 +1233,7 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Hot 🟩</t>
+          <t>Warm 🟨</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1273,68 +1241,62 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>POD 6 Cyber Telco Retail M&amp;E</t>
+          <t>POD 4 Banking Payments Insurance</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Walmart Inc.</t>
+          <t>PayPal Holdings</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>walmart.com</t>
+          <t>paypal.com</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Outbound Now — High ML Signal</t>
+          <t>Monitor — Trending Up</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>Director+ hiring; GPU/inference signal; +8 new ML roles WoW</t>
+          <t>GPU/inference signal</t>
         </is>
       </c>
       <c r="J10" s="3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>(USA) Principal, Data Scientist - Applied AI</t>
+          <t>Sr Machine Learning Engineer — Agentic Systems</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Payments</t>
         </is>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>648125</v>
+        <v>31797</v>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
@@ -1350,7 +1312,7 @@
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Hot 🟩</t>
+          <t>Warm 🟨</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -1363,43 +1325,39 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Netflix Inc.</t>
+          <t>Apple Inc.</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>netflix.com</t>
+          <t>apple.com</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Outbound Now — High ML Signal</t>
+          <t>Monitor — Trending Up</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>GPU/inference signal; +8 new ML roles WoW</t>
+          <t>GPU/inference signal</t>
         </is>
       </c>
       <c r="J11" s="3" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr"/>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -1408,16 +1366,16 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>Data Scientist 5 - TV &amp; Interactive Discovery</t>
+          <t>Machine Learning Engineer – Edge AI &amp; On-Device Optimization</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>Streaming</t>
+          <t>Consumer Tech</t>
         </is>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>39001</v>
+        <v>391035</v>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
@@ -1433,7 +1391,7 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Hot 🟩</t>
+          <t>Warm 🟨</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1446,43 +1404,39 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Uber Technologies</t>
+          <t>Intel Corporation</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>uber.com</t>
+          <t>intel.com</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Outbound Now — High ML Signal</t>
+          <t>Monitor — Trending Up</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>GPU/inference signal; +7 new ML roles WoW</t>
+          <t>GPU/inference signal</t>
         </is>
       </c>
       <c r="J12" s="3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -1491,16 +1445,16 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Applied AI</t>
+          <t>Senior GenAI Software Solutions Engineer</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>Mobility / Delivery</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>43970</v>
+        <v>53101</v>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
@@ -1516,7 +1470,7 @@
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Hot 🟩</t>
+          <t>Warm 🟨</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -1524,68 +1478,64 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>POD 5 Consumer Internet Software Auto</t>
+          <t>POD 6 Cyber Telco Retail M&amp;E</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>Walmart Inc.</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>microsoft.com</t>
+          <t>walmart.com</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Outbound Now — High ML Signal</t>
+          <t>Monitor — Trending Up</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>Director+ hiring; GPU/inference signal; +6 new ML roles WoW</t>
+          <t>Director+ hiring; GPU/inference signal</t>
         </is>
       </c>
       <c r="J13" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M13" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>Principal Applied Scientist (CoreAI)</t>
+          <t>(USA) Principal, Data Scientist - Applied AI</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>245122</v>
+        <v>648125</v>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
@@ -1601,7 +1551,7 @@
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Hot 🟩</t>
+          <t>Warm 🟨</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1609,68 +1559,60 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>POD 5 Consumer Internet Software Auto</t>
+          <t>POD 1 Capital Markets</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Oracle Corporation</t>
+          <t>BlackRock Inc.</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>oracle.com</t>
+          <t>blackrock.com</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Outbound Now — High ML Signal</t>
+          <t>Monitor — Trending Up</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>Director+ hiring; GPU/inference signal; +5 new ML roles WoW</t>
+          <t>Director+ hiring</t>
         </is>
       </c>
       <c r="J14" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>[Remote] Principal Applied Scientist</t>
+          <t>Alpha Generation Applied AI Engineer, Vice President</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>Software / Cloud</t>
+          <t>Asset Management</t>
         </is>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>52961</v>
+        <v>20407</v>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
@@ -1686,7 +1628,7 @@
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Hot 🟩</t>
+          <t>Warm 🟨</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -1694,66 +1636,58 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>POD 5 Consumer Internet Software Auto</t>
+          <t>POD 1 Capital Markets</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Salesforce Inc.</t>
+          <t>Intercontinental Exchange</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>salesforce.com</t>
+          <t>ice.com</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Outbound Now — High ML Signal</t>
+          <t>Monitor — Trending Up</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>GPU/inference signal; +5 new ML roles WoW</t>
+          <t>1 active ML roles</t>
         </is>
       </c>
       <c r="J15" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr"/>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>Lead AI Engineer, Data Solutions</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>SaaS</t>
+          <t>Exchanges</t>
         </is>
       </c>
       <c r="Q15" s="2" t="n">
-        <v>37895</v>
+        <v>9333</v>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
@@ -1769,7 +1703,7 @@
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Hot 🟩</t>
+          <t>Warm 🟨</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1777,66 +1711,58 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>POD 5 Consumer Internet Software Auto</t>
+          <t>POD 2 Healthcare &amp; Life Sciences</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Intel Corporation</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>intel.com</t>
+          <t>abbott.com</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Outbound Now — High ML Signal</t>
+          <t>Monitor — Trending Up</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>GPU/inference signal; +4 ML roles added</t>
+          <t>1 active ML roles</t>
         </is>
       </c>
       <c r="J16" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>Senior GenAI Software Solutions Engineer</t>
+          <t>Senior Clinical Research Scientist</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Medical Devices</t>
         </is>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>53101</v>
+        <v>41950</v>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
@@ -1852,7 +1778,7 @@
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Hot 🟩</t>
+          <t>Warm 🟨</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -1860,66 +1786,64 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>POD 6 Cyber Telco Retail M&amp;E</t>
+          <t>POD 2 Healthcare &amp; Life Sciences</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>T-Mobile US Inc.</t>
+          <t>AbbVie Inc.</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>t-mobile.com</t>
+          <t>abbvie.com</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Outbound Now — High ML Signal</t>
+          <t>Monitor — Trending Up</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>GPU/inference signal; +4 ML roles added</t>
+          <t>Director+ hiring; GPU/inference signal</t>
         </is>
       </c>
       <c r="J17" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr"/>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>T Hub - AI Intern – LLM, Voice to Text &amp; Agentic Systems</t>
+          <t>Principal Research Scientist II - Process Chemistry</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>Telco</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="Q17" s="2" t="n">
-        <v>81400</v>
+        <v>56334</v>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
@@ -1935,7 +1859,7 @@
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Hot 🟩</t>
+          <t>Warm 🟨</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1943,64 +1867,62 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>POD 6 Cyber Telco Retail M&amp;E</t>
+          <t>POD 2 Healthcare &amp; Life Sciences</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Target Corporation</t>
+          <t>Amgen Inc.</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>target.com</t>
+          <t>amgen.com</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Outbound Now — High ML Signal</t>
+          <t>Monitor — Trending Up</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>Director+ hiring; +3 ML roles added</t>
+          <t>GPU/inference signal</t>
         </is>
       </c>
       <c r="J18" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>Principal AI Engineer-Advanced AI</t>
+          <t>Sr Machine Learning Engineer</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Biotech</t>
         </is>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>107412</v>
+        <v>33424</v>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
@@ -2016,7 +1938,7 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Hot 🟩</t>
+          <t>Warm 🟨</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -2029,63 +1951,53 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Pfizer Inc.</t>
+          <t>Humana Inc.</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>pfizer.com</t>
+          <t>humana.com</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Outbound Now — High ML Signal</t>
+          <t>Monitor — Trending Up</t>
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>Director+ hiring; GPU/inference signal; +3 ML roles added</t>
+          <t>3 active ML roles</t>
         </is>
       </c>
       <c r="J19" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>Principal Statistical Data Scientist</t>
+          <t>Infrastructure Operations Lead Cloud and AI GenAI Enablement</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Managed Care</t>
         </is>
       </c>
       <c r="Q19" s="2" t="n">
-        <v>63627</v>
+        <v>117761</v>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
@@ -2101,7 +2013,7 @@
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Hot 🟩</t>
+          <t>Warm 🟨</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -2109,64 +2021,62 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>POD 1 Capital Markets</t>
+          <t>POD 3 Manufacturing &amp; Robotics</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>BlackRock Inc.</t>
+          <t>Boeing Company</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>blackrock.com</t>
+          <t>boeing.com</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>Outbound Now — High ML Signal</t>
+          <t>Monitor — Trending Up</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>Director+ hiring; +3 ML roles added</t>
+          <t>GPU/inference signal</t>
         </is>
       </c>
       <c r="J20" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M20" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>Alpha Generation Applied AI Engineer, Vice President</t>
+          <t>AI/ML Researcher (Multimodal)</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>Asset Management</t>
+          <t>Aerospace</t>
         </is>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>20407</v>
+        <v>77794</v>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
@@ -2182,7 +2092,7 @@
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Hot 🟩</t>
+          <t>Warm 🟨</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -2190,48 +2100,44 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>POD 2 Healthcare &amp; Life Sciences</t>
+          <t>POD 3 Manufacturing &amp; Robotics</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>AbbVie Inc.</t>
+          <t>Honeywell International</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>abbvie.com</t>
+          <t>honeywell.com</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Outbound Now — High ML Signal</t>
+          <t>Monitor — Trending Up</t>
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>Director+ hiring; GPU/inference signal; +3 ML roles added</t>
+          <t>Director+ hiring; GPU/inference signal</t>
         </is>
       </c>
       <c r="J21" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="L21" s="2" t="inlineStr"/>
       <c r="M21" s="2" t="n">
         <v>1</v>
       </c>
@@ -2242,16 +2148,16 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>Principal Research Scientist II - Process Chemistry</t>
+          <t>Principal AI Engineer</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Industrial Conglomerate</t>
         </is>
       </c>
       <c r="Q21" s="2" t="n">
-        <v>56334</v>
+        <v>37847</v>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
@@ -2267,7 +2173,7 @@
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Hot 🟩</t>
+          <t>Warm 🟨</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -2275,48 +2181,44 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>POD 2 Healthcare &amp; Life Sciences</t>
+          <t>POD 3 Manufacturing &amp; Robotics</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Amgen Inc.</t>
+          <t>Jacobs Solutions Inc.</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>amgen.com</t>
+          <t>jacobs.com</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>Outbound Now — High ML Signal</t>
+          <t>Monitor — Trending Up</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>GPU/inference signal; +3 ML roles added</t>
+          <t>GPU/inference signal</t>
         </is>
       </c>
       <c r="J22" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="L22" s="2" t="inlineStr"/>
       <c r="M22" s="2" t="inlineStr"/>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -2325,16 +2227,16 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer</t>
+          <t>Senior AI/Data Platform Engineer (Snowflake, GenAI)</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>Biotech</t>
+          <t>Engineering / Defense</t>
         </is>
       </c>
       <c r="Q22" s="2" t="n">
-        <v>33424</v>
+        <v>16751</v>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
@@ -2350,7 +2252,7 @@
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Hot 🟩</t>
+          <t>Warm 🟨</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
@@ -2358,62 +2260,58 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>POD 2 Healthcare &amp; Life Sciences</t>
+          <t>POD 4 Banking Payments Insurance</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Humana Inc.</t>
+          <t>AIG (American Intl. Group)</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>humana.com</t>
+          <t>aig.com</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Outbound Now — High ML Signal</t>
+          <t>Monitor — Trending Up</t>
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>+3 ML roles added</t>
+          <t>1 active ML roles</t>
         </is>
       </c>
       <c r="J23" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L23" s="2" t="inlineStr"/>
       <c r="M23" s="2" t="inlineStr"/>
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>Infrastructure Operations Lead Cloud and AI GenAI Enablement</t>
+          <t>Ph.D. Research Data Scientist, GenAI</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>Managed Care</t>
+          <t>P&amp;C Insurance</t>
         </is>
       </c>
       <c r="Q23" s="2" t="n">
-        <v>117761</v>
+        <v>46951</v>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
@@ -2429,7 +2327,7 @@
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Hot 🟩</t>
+          <t>Warm 🟨</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -2437,68 +2335,64 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>POD 3 Manufacturing &amp; Robotics</t>
+          <t>POD 4 Banking Payments Insurance</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Honeywell International</t>
+          <t>Citigroup Inc.</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>honeywell.com</t>
+          <t>citigroup.com</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>Outbound Now — High ML Signal</t>
+          <t>Monitor — Trending Up</t>
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>Director+ hiring; GPU/inference signal; +3 ML roles added</t>
+          <t>Director+ hiring; GPU/inference signal</t>
         </is>
       </c>
       <c r="J24" s="3" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
+        <v>18</v>
+      </c>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>Principal AI Engineer</t>
+          <t>Lead AI Engineer, Banking Technology - Senior Vice President</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>Industrial Conglomerate</t>
+          <t>Money Center Bank</t>
         </is>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>37847</v>
+        <v>71355</v>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
@@ -2514,7 +2408,7 @@
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Hot 🟩</t>
+          <t>Warm 🟨</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
@@ -2522,64 +2416,64 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>POD 6 Cyber Telco Retail M&amp;E</t>
+          <t>POD 4 Banking Payments Insurance</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Verizon Communications</t>
+          <t>Mastercard Incorporated</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>verizon.com</t>
+          <t>mastercard.com</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Outbound Now — High ML Signal</t>
+          <t>Monitor — Trending Up</t>
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>Director+ hiring; +3 ML roles added</t>
+          <t>Director+ hiring; GPU/inference signal</t>
         </is>
       </c>
       <c r="J25" s="3" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>Principal Data Scientist</t>
+          <t>Principal AI Engineer</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>Telco</t>
+          <t>Payment Networks</t>
         </is>
       </c>
       <c r="Q25" s="2" t="n">
-        <v>134788</v>
+        <v>28167</v>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
@@ -2595,7 +2489,7 @@
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Hot 🟩</t>
+          <t>Warm 🟨</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -2603,66 +2497,58 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>POD 3 Manufacturing &amp; Robotics</t>
+          <t>POD 4 Banking Payments Insurance</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Jacobs Solutions Inc.</t>
+          <t>Travelers Companies</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>jacobs.com</t>
+          <t>travelers.com</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Outbound Now — High ML Signal</t>
+          <t>Monitor — Trending Up</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>GPU/inference signal; +2 ML roles added</t>
+          <t>1 active ML roles</t>
         </is>
       </c>
       <c r="J26" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr"/>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>Senior AI/Data Platform Engineer (Snowflake, GenAI)</t>
+          <t>Senior Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>Engineering / Defense</t>
+          <t>P&amp;C Insurance</t>
         </is>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>16751</v>
+        <v>46421</v>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
@@ -2678,7 +2564,7 @@
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Hot 🟩</t>
+          <t>Warm 🟨</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
@@ -2701,33 +2587,29 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Outbound Now — High ML Signal</t>
+          <t>Monitor — Trending Up</t>
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>Director+ hiring; GPU/inference signal; +2 ML roles added</t>
+          <t>Director+ hiring; GPU/inference signal</t>
         </is>
       </c>
       <c r="J27" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="n">
         <v>1</v>
       </c>
@@ -2763,7 +2645,7 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Hot 🟩</t>
+          <t>Warm 🟨</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -2771,68 +2653,58 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>POD 6 Cyber Telco Retail M&amp;E</t>
+          <t>POD 5 Consumer Internet Software Auto</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Paramount Global</t>
+          <t>Comcast Corporation</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>paramount.com</t>
+          <t>corporate.comcast.com</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Outbound Now — High ML Signal</t>
+          <t>Monitor — Trending Up</t>
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>Director+ hiring; GPU/inference signal; +2 ML roles added</t>
+          <t>1 active ML roles</t>
         </is>
       </c>
       <c r="J28" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>Principal Machine Learning Engineer, Presentation and Visual Optimization</t>
+          <t>Engineer 4 - Machine Learning</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Cable / Media</t>
         </is>
       </c>
       <c r="Q28" s="2" t="n">
-        <v>29206</v>
+        <v>123731</v>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
@@ -2848,7 +2720,7 @@
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Hot 🟩</t>
+          <t>Warm 🟨</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
@@ -2856,48 +2728,44 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>POD 4 Banking Payments Insurance</t>
+          <t>POD 5 Consumer Internet Software Auto</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>PayPal Holdings</t>
+          <t>Netflix Inc.</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>paypal.com</t>
+          <t>netflix.com</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Outbound Now — High ML Signal</t>
+          <t>Monitor — Trending Up</t>
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>GPU/inference signal; +1 ML roles added</t>
+          <t>GPU/inference signal</t>
         </is>
       </c>
       <c r="J29" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr"/>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -2906,16 +2774,16 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer — Agentic Systems</t>
+          <t>Data Scientist 5 - TV &amp; Interactive Discovery</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>Payments</t>
+          <t>Streaming</t>
         </is>
       </c>
       <c r="Q29" s="2" t="n">
-        <v>31797</v>
+        <v>39001</v>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
@@ -2931,7 +2799,7 @@
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Hot 🟩</t>
+          <t>Warm 🟨</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -2939,62 +2807,62 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>POD 1 Capital Markets</t>
+          <t>POD 5 Consumer Internet Software Auto</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange</t>
+          <t>Qualcomm Inc.</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>ice.com</t>
+          <t>qualcomm.com</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Outbound Now — High ML Signal</t>
+          <t>Monitor — Trending Up</t>
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>+1 ML roles added</t>
+          <t>GPU/inference signal</t>
         </is>
       </c>
       <c r="J30" s="3" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
+        <v>29</v>
+      </c>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr"/>
-      <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>2026 Intern-Machine Learning &amp;Multimedia Software Engineer</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>Exchanges</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="Q30" s="2" t="n">
-        <v>9333</v>
+        <v>38962</v>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
@@ -3010,7 +2878,7 @@
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Hot 🟩</t>
+          <t>Warm 🟨</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
@@ -3018,62 +2886,62 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>POD 2 Healthcare &amp; Life Sciences</t>
+          <t>POD 5 Consumer Internet Software Auto</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Salesforce Inc.</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>abbott.com</t>
+          <t>salesforce.com</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>Outbound Now — High ML Signal</t>
+          <t>Monitor — Trending Up</t>
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>+1 ML roles added</t>
+          <t>GPU/inference signal</t>
         </is>
       </c>
       <c r="J31" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr"/>
-      <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>Senior Clinical Research Scientist</t>
+          <t>Lead AI Engineer, Data Solutions</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>Medical Devices</t>
+          <t>SaaS</t>
         </is>
       </c>
       <c r="Q31" s="2" t="n">
-        <v>41950</v>
+        <v>37895</v>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
@@ -3089,7 +2957,7 @@
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Hot 🟩</t>
+          <t>Warm 🟨</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -3097,66 +2965,58 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>POD 3 Manufacturing &amp; Robotics</t>
+          <t>POD 5 Consumer Internet Software Auto</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Boeing Company</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>boeing.com</t>
+          <t>stellantis.com</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Outbound Now — High ML Signal</t>
+          <t>Monitor — Trending Up</t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>GPU/inference signal; +1 ML roles added</t>
+          <t>1 active ML roles</t>
         </is>
       </c>
       <c r="J32" s="3" t="n">
         <v>1</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr"/>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>AI/ML Researcher (Multimodal)</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>Aerospace</t>
+          <t>Auto OEM</t>
         </is>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>77794</v>
+        <v>201202</v>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
@@ -3172,7 +3032,7 @@
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Hot 🟩</t>
+          <t>Warm 🟨</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
@@ -3180,62 +3040,62 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>POD 4 Banking Payments Insurance</t>
+          <t>POD 5 Consumer Internet Software Auto</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>AIG (American Intl. Group)</t>
+          <t>Tesla Inc.</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>aig.com</t>
+          <t>tesla.com</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>Outbound Now — High ML Signal</t>
+          <t>Monitor — Trending Up</t>
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>+1 ML roles added</t>
+          <t>GPU/inference signal</t>
         </is>
       </c>
       <c r="J33" s="3" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
+        <v>21</v>
+      </c>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M33" s="2" t="inlineStr"/>
-      <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>Ph.D. Research Data Scientist, GenAI</t>
+          <t>Site Reliability Engineer, HPC / AI Infrastructure</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>P&amp;C Insurance</t>
+          <t>EV / Auto</t>
         </is>
       </c>
       <c r="Q33" s="2" t="n">
-        <v>46951</v>
+        <v>97690</v>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
@@ -3251,7 +3111,7 @@
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Hot 🟩</t>
+          <t>Warm 🟨</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -3259,62 +3119,64 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>POD 4 Banking Payments Insurance</t>
+          <t>POD 6 Cyber Telco Retail M&amp;E</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Travelers Companies</t>
+          <t>Paramount Global</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>travelers.com</t>
+          <t>paramount.com</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Outbound Now — High ML Signal</t>
+          <t>Monitor — Trending Up</t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>Director+ hiring; GPU/inference signal</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K34" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t>+1 ML roles added</t>
-        </is>
-      </c>
-      <c r="J34" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M34" s="2" t="inlineStr"/>
-      <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Engineer</t>
+          <t>Principal Machine Learning Engineer, Presentation and Visual Optimization</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>P&amp;C Insurance</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="Q34" s="2" t="n">
-        <v>46421</v>
+        <v>29206</v>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
@@ -3330,7 +3192,7 @@
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Hot 🟩</t>
+          <t>Warm 🟨</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
@@ -3338,62 +3200,62 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>POD 5 Consumer Internet Software Auto</t>
+          <t>POD 6 Cyber Telco Retail M&amp;E</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Comcast Corporation</t>
+          <t>T-Mobile US Inc.</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>corporate.comcast.com</t>
+          <t>t-mobile.com</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>Outbound Now — High ML Signal</t>
+          <t>Monitor — Trending Up</t>
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>+1 ML roles added</t>
+          <t>GPU/inference signal</t>
         </is>
       </c>
       <c r="J35" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="M35" s="2" t="inlineStr"/>
-      <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>Engineer 4 - Machine Learning</t>
+          <t>T Hub - AI Intern – LLM, Voice to Text &amp; Agentic Systems</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>Cable / Media</t>
+          <t>Telco</t>
         </is>
       </c>
       <c r="Q35" s="2" t="n">
-        <v>123731</v>
+        <v>81400</v>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
@@ -3409,7 +3271,7 @@
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Hot 🟩</t>
+          <t>Warm 🟨</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -3417,62 +3279,60 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>POD 5 Consumer Internet Software Auto</t>
+          <t>POD 6 Cyber Telco Retail M&amp;E</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Verizon Communications</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>stellantis.com</t>
+          <t>verizon.com</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Outbound Now — High ML Signal</t>
+          <t>Monitor — Trending Up</t>
         </is>
       </c>
       <c r="G36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>Director+ hiring</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t>+1 ML roles added</t>
-        </is>
-      </c>
-      <c r="J36" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Principal Data Scientist</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>Auto OEM</t>
+          <t>Telco</t>
         </is>
       </c>
       <c r="Q36" s="2" t="n">
-        <v>201202</v>
+        <v>134788</v>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>

--- a/output/ML_Hires_Signal_2026-05-29.xlsx
+++ b/output/ML_Hires_Signal_2026-05-29.xlsx
@@ -2335,17 +2335,17 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>POD 4 Banking Payments Insurance</t>
+          <t>POD 6 Cyber Telco Retail M&amp;E</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Citigroup Inc.</t>
+          <t>Paramount Global</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>citigroup.com</t>
+          <t>paramount.com</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -2367,14 +2367,14 @@
         </is>
       </c>
       <c r="J24" s="3" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -2383,16 +2383,16 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>Lead AI Engineer, Banking Technology - Senior Vice President</t>
+          <t>Principal Machine Learning Engineer, Presentation and Visual Optimization</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>Money Center Bank</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>71355</v>
+        <v>29206</v>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
@@ -2416,17 +2416,17 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>POD 4 Banking Payments Insurance</t>
+          <t>POD 6 Cyber Telco Retail M&amp;E</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Mastercard Incorporated</t>
+          <t>T-Mobile US Inc.</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>mastercard.com</t>
+          <t>t-mobile.com</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -2444,19 +2444,17 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>Director+ hiring; GPU/inference signal</t>
+          <t>GPU/inference signal</t>
         </is>
       </c>
       <c r="J25" s="3" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L25" s="2" t="inlineStr"/>
-      <c r="M25" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M25" s="2" t="inlineStr"/>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2464,16 +2462,16 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>Principal AI Engineer</t>
+          <t>T Hub - AI Intern – LLM, Voice to Text &amp; Agentic Systems</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>Payment Networks</t>
+          <t>Telco</t>
         </is>
       </c>
       <c r="Q25" s="2" t="n">
-        <v>28167</v>
+        <v>81400</v>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
@@ -2497,17 +2495,17 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>POD 4 Banking Payments Insurance</t>
+          <t>POD 6 Cyber Telco Retail M&amp;E</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Travelers Companies</t>
+          <t>Verizon Communications</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>travelers.com</t>
+          <t>verizon.com</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -2525,30 +2523,32 @@
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>1 active ML roles</t>
+          <t>Director+ hiring</t>
         </is>
       </c>
       <c r="J26" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K26" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L26" s="2" t="inlineStr"/>
-      <c r="M26" s="2" t="inlineStr"/>
       <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Engineer</t>
+          <t>Principal Data Scientist</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>P&amp;C Insurance</t>
+          <t>Telco</t>
         </is>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>46421</v>
+        <v>134788</v>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
@@ -2562,784 +2562,750 @@
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Warm 🟨</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Quiet ⬜</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>POD 4 Banking Payments Insurance</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Capital One Financial</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>capitalone.com</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Hold</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="4" t="inlineStr"/>
+      <c r="M27" s="4" t="inlineStr"/>
+      <c r="N27" s="4" t="inlineStr"/>
+      <c r="O27" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P27" s="5" t="inlineStr">
+        <is>
+          <t>Consumer Bank</t>
+        </is>
+      </c>
+      <c r="Q27" s="4" t="n">
+        <v>39135</v>
+      </c>
+      <c r="R27" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S27" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Quiet ⬜</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>POD 5 Consumer Internet Software Auto</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>Cisco Systems Inc.</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>cisco.com</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>Monitor — Trending Up</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>Director+ hiring; GPU/inference signal</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K27" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L27" s="2" t="inlineStr"/>
-      <c r="M27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t>Principal Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="P27" s="3" t="inlineStr">
-        <is>
-          <t>Networking</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="n">
-        <v>53803</v>
-      </c>
-      <c r="R27" s="3" t="inlineStr">
-        <is>
-          <t>TheirStack</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Warm 🟨</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Amazon.com Inc.</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>amazon.com</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>Hold</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="4" t="inlineStr"/>
+      <c r="M28" s="4" t="inlineStr"/>
+      <c r="N28" s="4" t="inlineStr"/>
+      <c r="O28" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P28" s="5" t="inlineStr">
+        <is>
+          <t>E-commerce / Cloud</t>
+        </is>
+      </c>
+      <c r="Q28" s="4" t="n">
+        <v>637959</v>
+      </c>
+      <c r="R28" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S28" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Quiet ⬜</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>POD 5 Consumer Internet Software Auto</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>Comcast Corporation</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>corporate.comcast.com</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>Monitor — Trending Up</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>1 active ML roles</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K28" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L28" s="2" t="inlineStr"/>
-      <c r="M28" s="2" t="inlineStr"/>
-      <c r="N28" s="2" t="inlineStr"/>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t>Engineer 4 - Machine Learning</t>
-        </is>
-      </c>
-      <c r="P28" s="3" t="inlineStr">
-        <is>
-          <t>Cable / Media</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="n">
-        <v>123731</v>
-      </c>
-      <c r="R28" s="3" t="inlineStr">
-        <is>
-          <t>TheirStack</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>Warm 🟨</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>disney.com</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Hold</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="4" t="inlineStr"/>
+      <c r="M29" s="4" t="inlineStr"/>
+      <c r="N29" s="4" t="inlineStr"/>
+      <c r="O29" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P29" s="5" t="inlineStr">
+        <is>
+          <t>Media / Streaming</t>
+        </is>
+      </c>
+      <c r="Q29" s="4" t="n">
+        <v>91361</v>
+      </c>
+      <c r="R29" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S29" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Quiet ⬜</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>POD 2 Healthcare &amp; Life Sciences</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Eli Lilly and Company</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>lilly.com</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>Hold</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="4" t="inlineStr"/>
+      <c r="M30" s="4" t="inlineStr"/>
+      <c r="N30" s="4" t="inlineStr"/>
+      <c r="O30" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P30" s="5" t="inlineStr">
+        <is>
+          <t>Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="Q30" s="4" t="n">
+        <v>45042</v>
+      </c>
+      <c r="R30" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S30" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Quiet ⬜</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>POD 7 Higher Education</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Johns Hopkins University</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>jhu.edu</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Hold</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="4" t="inlineStr"/>
+      <c r="M31" s="4" t="inlineStr"/>
+      <c r="N31" s="4" t="inlineStr"/>
+      <c r="O31" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P31" s="5" t="inlineStr">
+        <is>
+          <t>R1 Research University</t>
+        </is>
+      </c>
+      <c r="Q31" s="4" t="n">
+        <v>3833</v>
+      </c>
+      <c r="R31" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S31" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Quiet ⬜</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>POD 2 Healthcare &amp; Life Sciences</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>Thermo Fisher Scientific</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>thermofisher.com</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>Hold</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="4" t="inlineStr"/>
+      <c r="M32" s="4" t="inlineStr"/>
+      <c r="N32" s="4" t="inlineStr"/>
+      <c r="O32" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P32" s="5" t="inlineStr">
+        <is>
+          <t>Life Sci Tools</t>
+        </is>
+      </c>
+      <c r="Q32" s="4" t="n">
+        <v>42857</v>
+      </c>
+      <c r="R32" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S32" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Quiet ⬜</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>POD 5 Consumer Internet Software Auto</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>Netflix Inc.</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>netflix.com</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>Monitor — Trending Up</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>GPU/inference signal</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="K29" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L29" s="2" t="inlineStr"/>
-      <c r="M29" s="2" t="inlineStr"/>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t>Data Scientist 5 - TV &amp; Interactive Discovery</t>
-        </is>
-      </c>
-      <c r="P29" s="3" t="inlineStr">
-        <is>
-          <t>Streaming</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="n">
-        <v>39001</v>
-      </c>
-      <c r="R29" s="3" t="inlineStr">
-        <is>
-          <t>TheirStack</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>Warm 🟨</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>POD 5 Consumer Internet Software Auto</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>Qualcomm Inc.</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>qualcomm.com</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>Monitor — Trending Up</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="inlineStr">
-        <is>
-          <t>GPU/inference signal</t>
-        </is>
-      </c>
-      <c r="J30" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="K30" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="L30" s="2" t="inlineStr"/>
-      <c r="M30" s="2" t="inlineStr"/>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O30" s="3" t="inlineStr">
-        <is>
-          <t>2026 Intern-Machine Learning &amp;Multimedia Software Engineer</t>
-        </is>
-      </c>
-      <c r="P30" s="3" t="inlineStr">
-        <is>
-          <t>Semiconductors</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="n">
-        <v>38962</v>
-      </c>
-      <c r="R30" s="3" t="inlineStr">
-        <is>
-          <t>TheirStack</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>Warm 🟨</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>POD 5 Consumer Internet Software Auto</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>Salesforce Inc.</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>salesforce.com</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>Monitor — Trending Up</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t>GPU/inference signal</t>
-        </is>
-      </c>
-      <c r="J31" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="K31" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="L31" s="2" t="inlineStr"/>
-      <c r="M31" s="2" t="inlineStr"/>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t>Lead AI Engineer, Data Solutions</t>
-        </is>
-      </c>
-      <c r="P31" s="3" t="inlineStr">
-        <is>
-          <t>SaaS</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="n">
-        <v>37895</v>
-      </c>
-      <c r="R31" s="3" t="inlineStr">
-        <is>
-          <t>TheirStack</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Warm 🟨</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>POD 5 Consumer Internet Software Auto</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>Stellantis N.V.</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>stellantis.com</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>Monitor — Trending Up</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t>1 active ML roles</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K32" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L32" s="2" t="inlineStr"/>
-      <c r="M32" s="2" t="inlineStr"/>
-      <c r="N32" s="2" t="inlineStr"/>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="P32" s="3" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Ford Motor Company</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>ford.com</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Hold</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="4" t="inlineStr"/>
+      <c r="M33" s="4" t="inlineStr"/>
+      <c r="N33" s="4" t="inlineStr"/>
+      <c r="O33" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P33" s="5" t="inlineStr">
         <is>
           <t>Auto OEM</t>
         </is>
       </c>
-      <c r="Q32" s="2" t="n">
-        <v>201202</v>
-      </c>
-      <c r="R32" s="3" t="inlineStr">
-        <is>
-          <t>TheirStack</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>Warm 🟨</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>POD 5 Consumer Internet Software Auto</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>Tesla Inc.</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>tesla.com</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>Monitor — Trending Up</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>GPU/inference signal</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="K33" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="L33" s="2" t="inlineStr"/>
-      <c r="M33" s="2" t="inlineStr"/>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer, HPC / AI Infrastructure</t>
-        </is>
-      </c>
-      <c r="P33" s="3" t="inlineStr">
-        <is>
-          <t>EV / Auto</t>
-        </is>
-      </c>
-      <c r="Q33" s="2" t="n">
-        <v>97690</v>
-      </c>
-      <c r="R33" s="3" t="inlineStr">
-        <is>
-          <t>TheirStack</t>
-        </is>
-      </c>
-      <c r="S33" s="2" t="inlineStr">
+      <c r="Q33" s="4" t="n">
+        <v>184992</v>
+      </c>
+      <c r="R33" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S33" s="4" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>Warm 🟨</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="n">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Quiet ⬜</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>POD 6 Cyber Telco Retail M&amp;E</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>Paramount Global</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>paramount.com</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>Monitor — Trending Up</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t>Director+ hiring; GPU/inference signal</t>
-        </is>
-      </c>
-      <c r="J34" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K34" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L34" s="2" t="inlineStr"/>
-      <c r="M34" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t>Principal Machine Learning Engineer, Presentation and Visual Optimization</t>
-        </is>
-      </c>
-      <c r="P34" s="3" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="n">
-        <v>29206</v>
-      </c>
-      <c r="R34" s="3" t="inlineStr">
-        <is>
-          <t>TheirStack</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>POD 2 Healthcare &amp; Life Sciences</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Merck &amp; Co. Inc.</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>merck.com</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>Hold</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="4" t="inlineStr"/>
+      <c r="M34" s="4" t="inlineStr"/>
+      <c r="N34" s="4" t="inlineStr"/>
+      <c r="O34" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P34" s="5" t="inlineStr">
+        <is>
+          <t>Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="Q34" s="4" t="n">
+        <v>64168</v>
+      </c>
+      <c r="R34" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S34" s="4" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>Warm 🟨</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="n">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Quiet ⬜</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>POD 6 Cyber Telco Retail M&amp;E</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>T-Mobile US Inc.</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>t-mobile.com</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>Monitor — Trending Up</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t>GPU/inference signal</t>
-        </is>
-      </c>
-      <c r="J35" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="K35" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="L35" s="2" t="inlineStr"/>
-      <c r="M35" s="2" t="inlineStr"/>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t>T Hub - AI Intern – LLM, Voice to Text &amp; Agentic Systems</t>
-        </is>
-      </c>
-      <c r="P35" s="3" t="inlineStr">
-        <is>
-          <t>Telco</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="n">
-        <v>81400</v>
-      </c>
-      <c r="R35" s="3" t="inlineStr">
-        <is>
-          <t>TheirStack</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>POD 7 Higher Education</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Texas A&amp;M University</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>tamu.edu</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Hold</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="4" t="inlineStr"/>
+      <c r="M35" s="4" t="inlineStr"/>
+      <c r="N35" s="4" t="inlineStr"/>
+      <c r="O35" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P35" s="5" t="inlineStr">
+        <is>
+          <t>R1 Research University</t>
+        </is>
+      </c>
+      <c r="Q35" s="4" t="n">
+        <v>1220</v>
+      </c>
+      <c r="R35" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S35" s="4" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Warm 🟨</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="n">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Quiet ⬜</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>POD 6 Cyber Telco Retail M&amp;E</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>Verizon Communications</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>verizon.com</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>Monitor — Trending Up</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t>Director+ hiring</t>
-        </is>
-      </c>
-      <c r="J36" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="K36" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="L36" s="2" t="inlineStr"/>
-      <c r="M36" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N36" s="2" t="inlineStr"/>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t>Principal Data Scientist</t>
-        </is>
-      </c>
-      <c r="P36" s="3" t="inlineStr">
-        <is>
-          <t>Telco</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="n">
-        <v>134788</v>
-      </c>
-      <c r="R36" s="3" t="inlineStr">
-        <is>
-          <t>TheirStack</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>POD 3 Manufacturing &amp; Robotics</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Northrop Grumman</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>northropgrumman.com</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>Hold</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="4" t="inlineStr"/>
+      <c r="M36" s="4" t="inlineStr"/>
+      <c r="N36" s="4" t="inlineStr"/>
+      <c r="O36" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P36" s="5" t="inlineStr">
+        <is>
+          <t>Defense</t>
+        </is>
+      </c>
+      <c r="Q36" s="4" t="n">
+        <v>40849</v>
+      </c>
+      <c r="R36" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S36" s="4" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -3356,17 +3322,17 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>POD 4 Banking Payments Insurance</t>
+          <t>POD 5 Consumer Internet Software Auto</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Capital One Financial</t>
+          <t>Meta Platforms Inc.</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>capitalone.com</t>
+          <t>meta.com</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
@@ -3403,11 +3369,11 @@
       </c>
       <c r="P37" s="5" t="inlineStr">
         <is>
-          <t>Consumer Bank</t>
+          <t>Social</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n">
-        <v>39135</v>
+        <v>164501</v>
       </c>
       <c r="R37" s="5" t="inlineStr">
         <is>
@@ -3431,17 +3397,17 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>POD 5 Consumer Internet Software Auto</t>
+          <t>POD 7 Higher Education</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Amazon.com Inc.</t>
+          <t>Stanford University</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>amazon.com</t>
+          <t>stanford.edu</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
@@ -3478,11 +3444,11 @@
       </c>
       <c r="P38" s="5" t="inlineStr">
         <is>
-          <t>E-commerce / Cloud</t>
+          <t>R1 Research University</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n">
-        <v>637959</v>
+        <v>1908</v>
       </c>
       <c r="R38" s="5" t="inlineStr">
         <is>
@@ -3506,17 +3472,17 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>POD 5 Consumer Internet Software Auto</t>
+          <t>POD 7 Higher Education</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Walt Disney Company</t>
+          <t>Duke University</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>disney.com</t>
+          <t>duke.edu</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
@@ -3553,11 +3519,11 @@
       </c>
       <c r="P39" s="5" t="inlineStr">
         <is>
-          <t>Media / Streaming</t>
+          <t>R1 Research University</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n">
-        <v>91361</v>
+        <v>1560</v>
       </c>
       <c r="R39" s="5" t="inlineStr">
         <is>
@@ -3581,17 +3547,17 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>POD 2 Healthcare &amp; Life Sciences</t>
+          <t>POD 1 Capital Markets</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Eli Lilly and Company</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>lilly.com</t>
+          <t>morganstanley.com</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
@@ -3628,11 +3594,11 @@
       </c>
       <c r="P40" s="5" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Investment Banking</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n">
-        <v>45042</v>
+        <v>54143</v>
       </c>
       <c r="R40" s="5" t="inlineStr">
         <is>
@@ -3656,17 +3622,17 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>POD 7 Higher Education</t>
+          <t>POD 1 Capital Markets</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Johns Hopkins University</t>
+          <t>Moody's Corporation</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>jhu.edu</t>
+          <t>moodys.com</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
@@ -3703,11 +3669,11 @@
       </c>
       <c r="P41" s="5" t="inlineStr">
         <is>
-          <t>R1 Research University</t>
+          <t>Ratings &amp; Analytics</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n">
-        <v>3833</v>
+        <v>7088</v>
       </c>
       <c r="R41" s="5" t="inlineStr">
         <is>
@@ -3736,12 +3702,12 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>UnitedHealth Group</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>thermofisher.com</t>
+          <t>unitedhealthgroup.com</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
@@ -3778,11 +3744,11 @@
       </c>
       <c r="P42" s="5" t="inlineStr">
         <is>
-          <t>Life Sci Tools</t>
+          <t>Managed Care</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n">
-        <v>42857</v>
+        <v>371622</v>
       </c>
       <c r="R42" s="5" t="inlineStr">
         <is>
@@ -3806,17 +3772,17 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>POD 5 Consumer Internet Software Auto</t>
+          <t>POD 2 Healthcare &amp; Life Sciences</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>ford.com</t>
+          <t>jnj.com</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
@@ -3853,11 +3819,11 @@
       </c>
       <c r="P43" s="5" t="inlineStr">
         <is>
-          <t>Auto OEM</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n">
-        <v>184992</v>
+        <v>88821</v>
       </c>
       <c r="R43" s="5" t="inlineStr">
         <is>
@@ -3881,17 +3847,17 @@
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>POD 2 Healthcare &amp; Life Sciences</t>
+          <t>POD 4 Banking Payments Insurance</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Merck &amp; Co. Inc.</t>
+          <t>Prudential Financial</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>merck.com</t>
+          <t>prudential.com</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
@@ -3928,11 +3894,11 @@
       </c>
       <c r="P44" s="5" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Life Insurance / Asset Mgmt</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n">
-        <v>64168</v>
+        <v>69991</v>
       </c>
       <c r="R44" s="5" t="inlineStr">
         <is>
@@ -3961,12 +3927,12 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Texas A&amp;M University</t>
+          <t>Columbia University</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>tamu.edu</t>
+          <t>columbia.edu</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
@@ -4003,11 +3969,11 @@
       </c>
       <c r="P45" s="5" t="inlineStr">
         <is>
-          <t>R1 Research University</t>
+          <t>Ivy League / R1</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n">
-        <v>1220</v>
+        <v>1389</v>
       </c>
       <c r="R45" s="5" t="inlineStr">
         <is>
@@ -4031,17 +3997,17 @@
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>POD 3 Manufacturing &amp; Robotics</t>
+          <t>POD 7 Higher Education</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Northrop Grumman</t>
+          <t>Cornell University</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>northropgrumman.com</t>
+          <t>cornell.edu</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
@@ -4078,11 +4044,11 @@
       </c>
       <c r="P46" s="5" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>Ivy League / R1</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n">
-        <v>40849</v>
+        <v>1369</v>
       </c>
       <c r="R46" s="5" t="inlineStr">
         <is>
@@ -4106,17 +4072,17 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>POD 5 Consumer Internet Software Auto</t>
+          <t>POD 7 Higher Education</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Meta Platforms Inc.</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>meta.com</t>
+          <t>gatech.edu</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
@@ -4153,11 +4119,11 @@
       </c>
       <c r="P47" s="5" t="inlineStr">
         <is>
-          <t>Social</t>
+          <t>R1 Research University</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n">
-        <v>164501</v>
+        <v>1357</v>
       </c>
       <c r="R47" s="5" t="inlineStr">
         <is>
@@ -4186,12 +4152,12 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>University of Florida</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>stanford.edu</t>
+          <t>ufl.edu</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
@@ -4232,7 +4198,7 @@
         </is>
       </c>
       <c r="Q48" s="4" t="n">
-        <v>1908</v>
+        <v>1240</v>
       </c>
       <c r="R48" s="5" t="inlineStr">
         <is>
@@ -4256,17 +4222,17 @@
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>POD 7 Higher Education</t>
+          <t>POD 1 Capital Markets</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Duke University</t>
+          <t>Ameriprise Financial</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>duke.edu</t>
+          <t>ameriprise.com</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
@@ -4303,11 +4269,11 @@
       </c>
       <c r="P49" s="5" t="inlineStr">
         <is>
-          <t>R1 Research University</t>
+          <t>Wealth Mgmt</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n">
-        <v>1560</v>
+        <v>16934</v>
       </c>
       <c r="R49" s="5" t="inlineStr">
         <is>
@@ -4336,12 +4302,12 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Apollo Global Management</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>morganstanley.com</t>
+          <t>apollo.com</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
@@ -4378,11 +4344,11 @@
       </c>
       <c r="P50" s="5" t="inlineStr">
         <is>
-          <t>Investment Banking</t>
+          <t>Alt Asset Mgmt</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n">
-        <v>54143</v>
+        <v>26113</v>
       </c>
       <c r="R50" s="5" t="inlineStr">
         <is>
@@ -4411,12 +4377,12 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Moody's Corporation</t>
+          <t>Bank of New York Mellon</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>moodys.com</t>
+          <t>bnymellon.com</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
@@ -4453,11 +4419,11 @@
       </c>
       <c r="P51" s="5" t="inlineStr">
         <is>
-          <t>Ratings &amp; Analytics</t>
+          <t>Custody / Trust</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n">
-        <v>7088</v>
+        <v>17779</v>
       </c>
       <c r="R51" s="5" t="inlineStr">
         <is>
@@ -4481,17 +4447,17 @@
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>POD 2 Healthcare &amp; Life Sciences</t>
+          <t>POD 1 Capital Markets</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>UnitedHealth Group</t>
+          <t>Blackstone Inc.</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>unitedhealthgroup.com</t>
+          <t>blackstone.com</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
@@ -4528,11 +4494,11 @@
       </c>
       <c r="P52" s="5" t="inlineStr">
         <is>
-          <t>Managed Care</t>
+          <t>Alt Asset Mgmt</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n">
-        <v>371622</v>
+        <v>11375</v>
       </c>
       <c r="R52" s="5" t="inlineStr">
         <is>
@@ -4556,17 +4522,17 @@
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>POD 2 Healthcare &amp; Life Sciences</t>
+          <t>POD 1 Capital Markets</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Brookfield Corporation</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>jnj.com</t>
+          <t>bn.brookfield.com</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
@@ -4603,11 +4569,11 @@
       </c>
       <c r="P53" s="5" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Alt Asset Mgmt</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n">
-        <v>88821</v>
+        <v>95061</v>
       </c>
       <c r="R53" s="5" t="inlineStr">
         <is>
@@ -4631,17 +4597,17 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>POD 4 Banking Payments Insurance</t>
+          <t>POD 1 Capital Markets</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Prudential Financial</t>
+          <t>Charles Schwab Corporation</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>prudential.com</t>
+          <t>schwab.com</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
@@ -4678,11 +4644,11 @@
       </c>
       <c r="P54" s="5" t="inlineStr">
         <is>
-          <t>Life Insurance / Asset Mgmt</t>
+          <t>Asset Mgmt / Brokerage</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n">
-        <v>69991</v>
+        <v>19600</v>
       </c>
       <c r="R54" s="5" t="inlineStr">
         <is>
@@ -4706,17 +4672,17 @@
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>POD 7 Higher Education</t>
+          <t>POD 1 Capital Markets</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Columbia University</t>
+          <t>Franklin Resources</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>columbia.edu</t>
+          <t>franklinresources.com</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
@@ -4753,11 +4719,11 @@
       </c>
       <c r="P55" s="5" t="inlineStr">
         <is>
-          <t>Ivy League / R1</t>
+          <t>Asset Management</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n">
-        <v>1389</v>
+        <v>8438</v>
       </c>
       <c r="R55" s="5" t="inlineStr">
         <is>
@@ -4781,17 +4747,17 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>POD 7 Higher Education</t>
+          <t>POD 1 Capital Markets</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>Goldman Sachs Group Inc.</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>cornell.edu</t>
+          <t>goldmansachs.com</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
@@ -4828,11 +4794,11 @@
       </c>
       <c r="P56" s="5" t="inlineStr">
         <is>
-          <t>Ivy League / R1</t>
+          <t>Investment Banking</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n">
-        <v>1369</v>
+        <v>53510</v>
       </c>
       <c r="R56" s="5" t="inlineStr">
         <is>
@@ -4856,17 +4822,17 @@
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>POD 7 Higher Education</t>
+          <t>POD 1 Capital Markets</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>Jefferies Financial Group</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>gatech.edu</t>
+          <t>jefferies.com</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
@@ -4903,11 +4869,11 @@
       </c>
       <c r="P57" s="5" t="inlineStr">
         <is>
-          <t>R1 Research University</t>
+          <t>Investment Banking</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n">
-        <v>1357</v>
+        <v>7013</v>
       </c>
       <c r="R57" s="5" t="inlineStr">
         <is>
@@ -4931,17 +4897,17 @@
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>POD 7 Higher Education</t>
+          <t>POD 1 Capital Markets</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>University of Florida</t>
+          <t>KKR &amp; Co. Inc.</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>ufl.edu</t>
+          <t>kkr.com</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
@@ -4978,11 +4944,11 @@
       </c>
       <c r="P58" s="5" t="inlineStr">
         <is>
-          <t>R1 Research University</t>
+          <t>Alt Asset Mgmt</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n">
-        <v>1240</v>
+        <v>15045</v>
       </c>
       <c r="R58" s="5" t="inlineStr">
         <is>
@@ -5011,12 +4977,12 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Ameriprise Financial</t>
+          <t>LPL Financial Holdings</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>ameriprise.com</t>
+          <t>lpl.com</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
@@ -5057,7 +5023,7 @@
         </is>
       </c>
       <c r="Q59" s="4" t="n">
-        <v>16934</v>
+        <v>11314</v>
       </c>
       <c r="R59" s="5" t="inlineStr">
         <is>
@@ -5086,12 +5052,12 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Apollo Global Management</t>
+          <t>Northern Trust Corporation</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>apollo.com</t>
+          <t>northerntrust.com</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
@@ -5128,11 +5094,11 @@
       </c>
       <c r="P60" s="5" t="inlineStr">
         <is>
-          <t>Alt Asset Mgmt</t>
+          <t>Custody / Trust</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n">
-        <v>26113</v>
+        <v>7339</v>
       </c>
       <c r="R60" s="5" t="inlineStr">
         <is>
@@ -5161,12 +5127,12 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Bank of New York Mellon</t>
+          <t>Raymond James Financial</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>bnymellon.com</t>
+          <t>raymondjames.com</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
@@ -5203,11 +5169,11 @@
       </c>
       <c r="P61" s="5" t="inlineStr">
         <is>
-          <t>Custody / Trust</t>
+          <t>Wealth Mgmt</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n">
-        <v>17779</v>
+        <v>12922</v>
       </c>
       <c r="R61" s="5" t="inlineStr">
         <is>
@@ -5236,12 +5202,12 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Blackstone Inc.</t>
+          <t>S&amp;P Global Inc.</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>blackstone.com</t>
+          <t>spglobal.com</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
@@ -5278,11 +5244,11 @@
       </c>
       <c r="P62" s="5" t="inlineStr">
         <is>
-          <t>Alt Asset Mgmt</t>
+          <t>Ratings &amp; Analytics</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n">
-        <v>11375</v>
+        <v>13439</v>
       </c>
       <c r="R62" s="5" t="inlineStr">
         <is>
@@ -5311,12 +5277,12 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>Brookfield Corporation</t>
+          <t>State Street Corporation</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>bn.brookfield.com</t>
+          <t>statestreet.com</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
@@ -5353,11 +5319,11 @@
       </c>
       <c r="P63" s="5" t="inlineStr">
         <is>
-          <t>Alt Asset Mgmt</t>
+          <t>Custody / Trust</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n">
-        <v>95061</v>
+        <v>11939</v>
       </c>
       <c r="R63" s="5" t="inlineStr">
         <is>
@@ -5386,12 +5352,12 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Charles Schwab Corporation</t>
+          <t>T. Rowe Price Group</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>schwab.com</t>
+          <t>troweprice.com</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
@@ -5428,11 +5394,11 @@
       </c>
       <c r="P64" s="5" t="inlineStr">
         <is>
-          <t>Asset Mgmt / Brokerage</t>
+          <t>Asset Management</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n">
-        <v>19600</v>
+        <v>7090</v>
       </c>
       <c r="R64" s="5" t="inlineStr">
         <is>
@@ -5456,17 +5422,17 @@
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>POD 1 Capital Markets</t>
+          <t>POD 2 Healthcare &amp; Life Sciences</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>Franklin Resources</t>
+          <t>Bristol-Myers Squibb</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>franklinresources.com</t>
+          <t>bms.com</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
@@ -5503,11 +5469,11 @@
       </c>
       <c r="P65" s="5" t="inlineStr">
         <is>
-          <t>Asset Management</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n">
-        <v>8438</v>
+        <v>48300</v>
       </c>
       <c r="R65" s="5" t="inlineStr">
         <is>
@@ -5531,17 +5497,17 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>POD 1 Capital Markets</t>
+          <t>POD 2 Healthcare &amp; Life Sciences</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Goldman Sachs Group Inc.</t>
+          <t>Cardinal Health Inc.</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>goldmansachs.com</t>
+          <t>cardinalhealth.com</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
@@ -5578,11 +5544,11 @@
       </c>
       <c r="P66" s="5" t="inlineStr">
         <is>
-          <t>Investment Banking</t>
+          <t>Drug Distribution</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n">
-        <v>53510</v>
+        <v>226828</v>
       </c>
       <c r="R66" s="5" t="inlineStr">
         <is>
@@ -5606,17 +5572,17 @@
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>POD 1 Capital Markets</t>
+          <t>POD 2 Healthcare &amp; Life Sciences</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>Jefferies Financial Group</t>
+          <t>Cencora Inc.</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>jefferies.com</t>
+          <t>cencora.com</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
@@ -5653,11 +5619,11 @@
       </c>
       <c r="P67" s="5" t="inlineStr">
         <is>
-          <t>Investment Banking</t>
+          <t>Drug Distribution</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n">
-        <v>7013</v>
+        <v>294041</v>
       </c>
       <c r="R67" s="5" t="inlineStr">
         <is>
@@ -5681,17 +5647,17 @@
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>POD 1 Capital Markets</t>
+          <t>POD 2 Healthcare &amp; Life Sciences</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>KKR &amp; Co. Inc.</t>
+          <t>Centene Corporation</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>kkr.com</t>
+          <t>centene.com</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
@@ -5728,11 +5694,11 @@
       </c>
       <c r="P68" s="5" t="inlineStr">
         <is>
-          <t>Alt Asset Mgmt</t>
+          <t>Managed Care</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n">
-        <v>15045</v>
+        <v>154000</v>
       </c>
       <c r="R68" s="5" t="inlineStr">
         <is>
@@ -5756,17 +5722,17 @@
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>POD 1 Capital Markets</t>
+          <t>POD 2 Healthcare &amp; Life Sciences</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>LPL Financial Holdings</t>
+          <t>Cigna Group</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>lpl.com</t>
+          <t>cigna.com</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
@@ -5803,11 +5769,11 @@
       </c>
       <c r="P69" s="5" t="inlineStr">
         <is>
-          <t>Wealth Mgmt</t>
+          <t>Managed Care</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n">
-        <v>11314</v>
+        <v>240931</v>
       </c>
       <c r="R69" s="5" t="inlineStr">
         <is>
@@ -5831,17 +5797,17 @@
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>POD 1 Capital Markets</t>
+          <t>POD 2 Healthcare &amp; Life Sciences</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Northern Trust Corporation</t>
+          <t>CVS Health Corporation</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>northerntrust.com</t>
+          <t>cvshealth.com</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
@@ -5878,11 +5844,11 @@
       </c>
       <c r="P70" s="5" t="inlineStr">
         <is>
-          <t>Custody / Trust</t>
+          <t>Pharmacy / PBM</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n">
-        <v>7339</v>
+        <v>372807</v>
       </c>
       <c r="R70" s="5" t="inlineStr">
         <is>
@@ -5906,17 +5872,17 @@
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>POD 1 Capital Markets</t>
+          <t>POD 2 Healthcare &amp; Life Sciences</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>Raymond James Financial</t>
+          <t>Elevance Health Inc.</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>raymondjames.com</t>
+          <t>elevancehealth.com</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
@@ -5953,11 +5919,11 @@
       </c>
       <c r="P71" s="5" t="inlineStr">
         <is>
-          <t>Wealth Mgmt</t>
+          <t>Managed Care</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n">
-        <v>12922</v>
+        <v>176815</v>
       </c>
       <c r="R71" s="5" t="inlineStr">
         <is>
@@ -5981,17 +5947,17 @@
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>POD 1 Capital Markets</t>
+          <t>POD 2 Healthcare &amp; Life Sciences</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>S&amp;P Global Inc.</t>
+          <t>Gilead Sciences</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>spglobal.com</t>
+          <t>gilead.com</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
@@ -6028,11 +5994,11 @@
       </c>
       <c r="P72" s="5" t="inlineStr">
         <is>
-          <t>Ratings &amp; Analytics</t>
+          <t>Biotech</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n">
-        <v>13439</v>
+        <v>28754</v>
       </c>
       <c r="R72" s="5" t="inlineStr">
         <is>
@@ -6056,17 +6022,17 @@
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>POD 1 Capital Markets</t>
+          <t>POD 2 Healthcare &amp; Life Sciences</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>State Street Corporation</t>
+          <t>HCA Healthcare Inc.</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>statestreet.com</t>
+          <t>hcahealthcare.com</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
@@ -6103,11 +6069,11 @@
       </c>
       <c r="P73" s="5" t="inlineStr">
         <is>
-          <t>Custody / Trust</t>
+          <t>Hospitals</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n">
-        <v>11939</v>
+        <v>67871</v>
       </c>
       <c r="R73" s="5" t="inlineStr">
         <is>
@@ -6131,17 +6097,17 @@
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>POD 1 Capital Markets</t>
+          <t>POD 2 Healthcare &amp; Life Sciences</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>T. Rowe Price Group</t>
+          <t>McKesson Corporation</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>troweprice.com</t>
+          <t>mckesson.com</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
@@ -6178,11 +6144,11 @@
       </c>
       <c r="P74" s="5" t="inlineStr">
         <is>
-          <t>Asset Management</t>
+          <t>Drug Distribution</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n">
-        <v>7090</v>
+        <v>309014</v>
       </c>
       <c r="R74" s="5" t="inlineStr">
         <is>
@@ -6206,17 +6172,17 @@
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>POD 2 Healthcare &amp; Life Sciences</t>
+          <t>POD 3 Manufacturing &amp; Robotics</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb</t>
+          <t>3M Company</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>bms.com</t>
+          <t>3m.com</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
@@ -6253,11 +6219,11 @@
       </c>
       <c r="P75" s="5" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Industrial Conglomerate</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n">
-        <v>48300</v>
+        <v>24575</v>
       </c>
       <c r="R75" s="5" t="inlineStr">
         <is>
@@ -6281,17 +6247,17 @@
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>POD 2 Healthcare &amp; Life Sciences</t>
+          <t>POD 3 Manufacturing &amp; Robotics</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Cardinal Health Inc.</t>
+          <t>Carrier Global</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>cardinalhealth.com</t>
+          <t>carrier.com</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
@@ -6328,11 +6294,11 @@
       </c>
       <c r="P76" s="5" t="inlineStr">
         <is>
-          <t>Drug Distribution</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n">
-        <v>226828</v>
+        <v>22489</v>
       </c>
       <c r="R76" s="5" t="inlineStr">
         <is>
@@ -6356,17 +6322,17 @@
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>POD 2 Healthcare &amp; Life Sciences</t>
+          <t>POD 3 Manufacturing &amp; Robotics</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>Cencora Inc.</t>
+          <t>Caterpillar Inc.</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>cencora.com</t>
+          <t>caterpillar.com</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
@@ -6403,11 +6369,11 @@
       </c>
       <c r="P77" s="5" t="inlineStr">
         <is>
-          <t>Drug Distribution</t>
+          <t>Heavy Equipment</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n">
-        <v>294041</v>
+        <v>64809</v>
       </c>
       <c r="R77" s="5" t="inlineStr">
         <is>
@@ -6431,17 +6397,17 @@
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>POD 2 Healthcare &amp; Life Sciences</t>
+          <t>POD 3 Manufacturing &amp; Robotics</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>Centene Corporation</t>
+          <t>Cummins Inc.</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>centene.com</t>
+          <t>cummins.com</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
@@ -6478,11 +6444,11 @@
       </c>
       <c r="P78" s="5" t="inlineStr">
         <is>
-          <t>Managed Care</t>
+          <t>Engines / Power</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n">
-        <v>154000</v>
+        <v>34102</v>
       </c>
       <c r="R78" s="5" t="inlineStr">
         <is>
@@ -6506,17 +6472,17 @@
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>POD 2 Healthcare &amp; Life Sciences</t>
+          <t>POD 3 Manufacturing &amp; Robotics</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>Cigna Group</t>
+          <t>Deere &amp; Company</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>cigna.com</t>
+          <t>deere.com</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
@@ -6553,11 +6519,11 @@
       </c>
       <c r="P79" s="5" t="inlineStr">
         <is>
-          <t>Managed Care</t>
+          <t>Agri Equipment</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n">
-        <v>240931</v>
+        <v>51716</v>
       </c>
       <c r="R79" s="5" t="inlineStr">
         <is>
@@ -6581,17 +6547,17 @@
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>POD 2 Healthcare &amp; Life Sciences</t>
+          <t>POD 3 Manufacturing &amp; Robotics</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>CVS Health Corporation</t>
+          <t>Eaton Corporation</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>cvshealth.com</t>
+          <t>eaton.com</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
@@ -6628,11 +6594,11 @@
       </c>
       <c r="P80" s="5" t="inlineStr">
         <is>
-          <t>Pharmacy / PBM</t>
+          <t>Power Mgmt</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n">
-        <v>372807</v>
+        <v>24879</v>
       </c>
       <c r="R80" s="5" t="inlineStr">
         <is>
@@ -6656,17 +6622,17 @@
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>POD 2 Healthcare &amp; Life Sciences</t>
+          <t>POD 3 Manufacturing &amp; Robotics</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>Elevance Health Inc.</t>
+          <t>Emerson Electric Co.</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>elevancehealth.com</t>
+          <t>emerson.com</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
@@ -6703,11 +6669,11 @@
       </c>
       <c r="P81" s="5" t="inlineStr">
         <is>
-          <t>Managed Care</t>
+          <t>Automation</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n">
-        <v>176815</v>
+        <v>17492</v>
       </c>
       <c r="R81" s="5" t="inlineStr">
         <is>
@@ -6731,17 +6697,17 @@
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>POD 2 Healthcare &amp; Life Sciences</t>
+          <t>POD 3 Manufacturing &amp; Robotics</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>Gilead Sciences</t>
+          <t>GE Vernova Inc.</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>gilead.com</t>
+          <t>gevernova.com</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
@@ -6778,11 +6744,11 @@
       </c>
       <c r="P82" s="5" t="inlineStr">
         <is>
-          <t>Biotech</t>
+          <t>Power &amp; Energy</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n">
-        <v>28754</v>
+        <v>34935</v>
       </c>
       <c r="R82" s="5" t="inlineStr">
         <is>
@@ -6806,17 +6772,17 @@
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>POD 2 Healthcare &amp; Life Sciences</t>
+          <t>POD 3 Manufacturing &amp; Robotics</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>HCA Healthcare Inc.</t>
+          <t>General Dynamics</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>hcahealthcare.com</t>
+          <t>gd.com</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
@@ -6853,11 +6819,11 @@
       </c>
       <c r="P83" s="5" t="inlineStr">
         <is>
-          <t>Hospitals</t>
+          <t>Defense</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n">
-        <v>67871</v>
+        <v>47716</v>
       </c>
       <c r="R83" s="5" t="inlineStr">
         <is>
@@ -6881,17 +6847,17 @@
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>POD 2 Healthcare &amp; Life Sciences</t>
+          <t>POD 3 Manufacturing &amp; Robotics</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>McKesson Corporation</t>
+          <t>General Electric Aerospace</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>mckesson.com</t>
+          <t>ge.com</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
@@ -6928,11 +6894,11 @@
       </c>
       <c r="P84" s="5" t="inlineStr">
         <is>
-          <t>Drug Distribution</t>
+          <t>Aerospace</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n">
-        <v>309014</v>
+        <v>38702</v>
       </c>
       <c r="R84" s="5" t="inlineStr">
         <is>
@@ -6961,12 +6927,12 @@
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>3M Company</t>
+          <t>L3Harris Technologies</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>3m.com</t>
+          <t>l3harris.com</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
@@ -7003,11 +6969,11 @@
       </c>
       <c r="P85" s="5" t="inlineStr">
         <is>
-          <t>Industrial Conglomerate</t>
+          <t>Defense</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n">
-        <v>24575</v>
+        <v>21321</v>
       </c>
       <c r="R85" s="5" t="inlineStr">
         <is>
@@ -7036,12 +7002,12 @@
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>Carrier Global</t>
+          <t>Lockheed Martin Corp.</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>carrier.com</t>
+          <t>lockheedmartin.com</t>
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr">
@@ -7078,11 +7044,11 @@
       </c>
       <c r="P86" s="5" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Defense</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n">
-        <v>22489</v>
+        <v>71043</v>
       </c>
       <c r="R86" s="5" t="inlineStr">
         <is>
@@ -7111,12 +7077,12 @@
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>Caterpillar Inc.</t>
+          <t>PACCAR Inc.</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
-          <t>caterpillar.com</t>
+          <t>paccar.com</t>
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr">
@@ -7153,11 +7119,11 @@
       </c>
       <c r="P87" s="5" t="inlineStr">
         <is>
-          <t>Heavy Equipment</t>
+          <t>Trucks</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n">
-        <v>64809</v>
+        <v>33656</v>
       </c>
       <c r="R87" s="5" t="inlineStr">
         <is>
@@ -7186,12 +7152,12 @@
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>Cummins Inc.</t>
+          <t>Parker-Hannifin</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>cummins.com</t>
+          <t>parker.com</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr">
@@ -7228,11 +7194,11 @@
       </c>
       <c r="P88" s="5" t="inlineStr">
         <is>
-          <t>Engines / Power</t>
+          <t>Industrial Machinery</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n">
-        <v>34102</v>
+        <v>19930</v>
       </c>
       <c r="R88" s="5" t="inlineStr">
         <is>
@@ -7261,12 +7227,12 @@
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>Deere &amp; Company</t>
+          <t>RTX Corporation</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>deere.com</t>
+          <t>rtx.com</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
@@ -7303,11 +7269,11 @@
       </c>
       <c r="P89" s="5" t="inlineStr">
         <is>
-          <t>Agri Equipment</t>
+          <t>Defense</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n">
-        <v>51716</v>
+        <v>80738</v>
       </c>
       <c r="R89" s="5" t="inlineStr">
         <is>
@@ -7336,12 +7302,12 @@
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>Eaton Corporation</t>
+          <t>Trane Technologies</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>eaton.com</t>
+          <t>tranetechnologies.com</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr">
@@ -7378,11 +7344,11 @@
       </c>
       <c r="P90" s="5" t="inlineStr">
         <is>
-          <t>Power Mgmt</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n">
-        <v>24879</v>
+        <v>19829</v>
       </c>
       <c r="R90" s="5" t="inlineStr">
         <is>
@@ -7406,17 +7372,17 @@
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>POD 3 Manufacturing &amp; Robotics</t>
+          <t>POD 4 Banking Payments Insurance</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>Emerson Electric Co.</t>
+          <t>Allstate Corporation</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>emerson.com</t>
+          <t>allstate.com</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
@@ -7453,11 +7419,11 @@
       </c>
       <c r="P91" s="5" t="inlineStr">
         <is>
-          <t>Automation</t>
+          <t>Auto/Home Insurance</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n">
-        <v>17492</v>
+        <v>64104</v>
       </c>
       <c r="R91" s="5" t="inlineStr">
         <is>
@@ -7481,17 +7447,17 @@
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>POD 3 Manufacturing &amp; Robotics</t>
+          <t>POD 4 Banking Payments Insurance</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>GE Vernova Inc.</t>
+          <t>American Express Company</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>gevernova.com</t>
+          <t>americanexpress.com</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr">
@@ -7528,11 +7494,11 @@
       </c>
       <c r="P92" s="5" t="inlineStr">
         <is>
-          <t>Power &amp; Energy</t>
+          <t>Payments</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n">
-        <v>34935</v>
+        <v>65454</v>
       </c>
       <c r="R92" s="5" t="inlineStr">
         <is>
@@ -7556,17 +7522,17 @@
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>POD 3 Manufacturing &amp; Robotics</t>
+          <t>POD 4 Banking Payments Insurance</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>General Dynamics</t>
+          <t>Bank of America Corp.</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>gd.com</t>
+          <t>bankofamerica.com</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
@@ -7603,11 +7569,11 @@
       </c>
       <c r="P93" s="5" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>Money Center Bank</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n">
-        <v>47716</v>
+        <v>98581</v>
       </c>
       <c r="R93" s="5" t="inlineStr">
         <is>
@@ -7631,17 +7597,17 @@
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>POD 3 Manufacturing &amp; Robotics</t>
+          <t>POD 4 Banking Payments Insurance</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>General Electric Aerospace</t>
+          <t>Berkshire Hathaway Inc.</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>ge.com</t>
+          <t>berkshirehathaway.com</t>
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr">
@@ -7678,11 +7644,11 @@
       </c>
       <c r="P94" s="5" t="inlineStr">
         <is>
-          <t>Aerospace</t>
+          <t>Diversified Insurance</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n">
-        <v>38702</v>
+        <v>371433</v>
       </c>
       <c r="R94" s="5" t="inlineStr">
         <is>
@@ -7706,17 +7672,17 @@
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>POD 3 Manufacturing &amp; Robotics</t>
+          <t>POD 4 Banking Payments Insurance</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>L3Harris Technologies</t>
+          <t>Block Inc.</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
         <is>
-          <t>l3harris.com</t>
+          <t>block.xyz</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
@@ -7753,11 +7719,11 @@
       </c>
       <c r="P95" s="5" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>Payments</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n">
-        <v>21321</v>
+        <v>24121</v>
       </c>
       <c r="R95" s="5" t="inlineStr">
         <is>
@@ -7781,17 +7747,17 @@
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>POD 3 Manufacturing &amp; Robotics</t>
+          <t>POD 4 Banking Payments Insurance</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>Lockheed Martin Corp.</t>
+          <t>Chubb Limited</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>lockheedmartin.com</t>
+          <t>chubb.com</t>
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr">
@@ -7828,11 +7794,11 @@
       </c>
       <c r="P96" s="5" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>P&amp;C Insurance</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n">
-        <v>71043</v>
+        <v>55400</v>
       </c>
       <c r="R96" s="5" t="inlineStr">
         <is>
@@ -7856,17 +7822,17 @@
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>POD 3 Manufacturing &amp; Robotics</t>
+          <t>POD 4 Banking Payments Insurance</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>PACCAR Inc.</t>
+          <t>Hartford Financial Services</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
         <is>
-          <t>paccar.com</t>
+          <t>thehartford.com</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr">
@@ -7903,11 +7869,11 @@
       </c>
       <c r="P97" s="5" t="inlineStr">
         <is>
-          <t>Trucks</t>
+          <t>P&amp;C Insurance</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n">
-        <v>33656</v>
+        <v>24341</v>
       </c>
       <c r="R97" s="5" t="inlineStr">
         <is>
@@ -7931,17 +7897,17 @@
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>POD 3 Manufacturing &amp; Robotics</t>
+          <t>POD 4 Banking Payments Insurance</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>Parker-Hannifin</t>
+          <t>MetLife Inc.</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>parker.com</t>
+          <t>metlife.com</t>
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr">
@@ -7978,11 +7944,11 @@
       </c>
       <c r="P98" s="5" t="inlineStr">
         <is>
-          <t>Industrial Machinery</t>
+          <t>Life Insurance</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n">
-        <v>19930</v>
+        <v>71008</v>
       </c>
       <c r="R98" s="5" t="inlineStr">
         <is>
@@ -8006,17 +7972,17 @@
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>POD 3 Manufacturing &amp; Robotics</t>
+          <t>POD 4 Banking Payments Insurance</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>RTX Corporation</t>
+          <t>Progressive Corporation</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
         <is>
-          <t>rtx.com</t>
+          <t>progressive.com</t>
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr">
@@ -8053,11 +8019,11 @@
       </c>
       <c r="P99" s="5" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>Auto Insurance</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n">
-        <v>80738</v>
+        <v>75342</v>
       </c>
       <c r="R99" s="5" t="inlineStr">
         <is>
@@ -8081,17 +8047,17 @@
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>POD 3 Manufacturing &amp; Robotics</t>
+          <t>POD 4 Banking Payments Insurance</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>Trane Technologies</t>
+          <t>U.S. Bancorp</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>tranetechnologies.com</t>
+          <t>usbank.com</t>
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr">
@@ -8128,11 +8094,11 @@
       </c>
       <c r="P100" s="5" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Regional Bank</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n">
-        <v>19829</v>
+        <v>40496</v>
       </c>
       <c r="R100" s="5" t="inlineStr">
         <is>
@@ -8161,12 +8127,12 @@
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>Allstate Corporation</t>
+          <t>Wells Fargo &amp; Company</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>allstate.com</t>
+          <t>wellsfargo.com</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
@@ -8203,11 +8169,11 @@
       </c>
       <c r="P101" s="5" t="inlineStr">
         <is>
-          <t>Auto/Home Insurance</t>
+          <t>Money Center Bank</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n">
-        <v>64104</v>
+        <v>82596</v>
       </c>
       <c r="R101" s="5" t="inlineStr">
         <is>
@@ -8231,17 +8197,17 @@
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>POD 4 Banking Payments Insurance</t>
+          <t>POD 5 Consumer Internet Software Auto</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>American Express Company</t>
+          <t>Alphabet Inc.</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>americanexpress.com</t>
+          <t>abc.xyz</t>
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr">
@@ -8278,11 +8244,11 @@
       </c>
       <c r="P102" s="5" t="inlineStr">
         <is>
-          <t>Payments</t>
+          <t>Search / Cloud</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n">
-        <v>65454</v>
+        <v>350018</v>
       </c>
       <c r="R102" s="5" t="inlineStr">
         <is>
@@ -8306,17 +8272,17 @@
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>POD 4 Banking Payments Insurance</t>
+          <t>POD 5 Consumer Internet Software Auto</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>Bank of America Corp.</t>
+          <t>Broadcom Inc.</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
         <is>
-          <t>bankofamerica.com</t>
+          <t>broadcom.com</t>
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr">
@@ -8353,11 +8319,11 @@
       </c>
       <c r="P103" s="5" t="inlineStr">
         <is>
-          <t>Money Center Bank</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n">
-        <v>98581</v>
+        <v>51574</v>
       </c>
       <c r="R103" s="5" t="inlineStr">
         <is>
@@ -8381,17 +8347,17 @@
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>POD 4 Banking Payments Insurance</t>
+          <t>POD 5 Consumer Internet Software Auto</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Inc.</t>
+          <t>General Motors Company</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>berkshirehathaway.com</t>
+          <t>gm.com</t>
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr">
@@ -8428,11 +8394,11 @@
       </c>
       <c r="P104" s="5" t="inlineStr">
         <is>
-          <t>Diversified Insurance</t>
+          <t>Auto OEM</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n">
-        <v>371433</v>
+        <v>187442</v>
       </c>
       <c r="R104" s="5" t="inlineStr">
         <is>
@@ -8456,17 +8422,17 @@
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>POD 4 Banking Payments Insurance</t>
+          <t>POD 6 Cyber Telco Retail M&amp;E</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>Block Inc.</t>
+          <t>AT&amp;T Inc.</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
         <is>
-          <t>block.xyz</t>
+          <t>att.com</t>
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr">
@@ -8503,11 +8469,11 @@
       </c>
       <c r="P105" s="5" t="inlineStr">
         <is>
-          <t>Payments</t>
+          <t>Telco</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n">
-        <v>24121</v>
+        <v>122336</v>
       </c>
       <c r="R105" s="5" t="inlineStr">
         <is>
@@ -8531,17 +8497,17 @@
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>POD 4 Banking Payments Insurance</t>
+          <t>POD 6 Cyber Telco Retail M&amp;E</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>Chubb Limited</t>
+          <t>Best Buy Co.</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>chubb.com</t>
+          <t>bestbuy.com</t>
         </is>
       </c>
       <c r="F106" s="5" t="inlineStr">
@@ -8578,11 +8544,11 @@
       </c>
       <c r="P106" s="5" t="inlineStr">
         <is>
-          <t>P&amp;C Insurance</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n">
-        <v>55400</v>
+        <v>41528</v>
       </c>
       <c r="R106" s="5" t="inlineStr">
         <is>
@@ -8606,17 +8572,17 @@
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>POD 4 Banking Payments Insurance</t>
+          <t>POD 6 Cyber Telco Retail M&amp;E</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>Hartford Financial Services</t>
+          <t>Charter Communications</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
         <is>
-          <t>thehartford.com</t>
+          <t>corporate.charter.com</t>
         </is>
       </c>
       <c r="F107" s="5" t="inlineStr">
@@ -8653,11 +8619,11 @@
       </c>
       <c r="P107" s="5" t="inlineStr">
         <is>
-          <t>P&amp;C Insurance</t>
+          <t>Cable</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n">
-        <v>24341</v>
+        <v>55085</v>
       </c>
       <c r="R107" s="5" t="inlineStr">
         <is>
@@ -8681,17 +8647,17 @@
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>POD 4 Banking Payments Insurance</t>
+          <t>POD 6 Cyber Telco Retail M&amp;E</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>MetLife Inc.</t>
+          <t>Costco Wholesale</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>metlife.com</t>
+          <t>costco.com</t>
         </is>
       </c>
       <c r="F108" s="5" t="inlineStr">
@@ -8728,11 +8694,11 @@
       </c>
       <c r="P108" s="5" t="inlineStr">
         <is>
-          <t>Life Insurance</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n">
-        <v>71008</v>
+        <v>254453</v>
       </c>
       <c r="R108" s="5" t="inlineStr">
         <is>
@@ -8756,17 +8722,17 @@
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>POD 4 Banking Payments Insurance</t>
+          <t>POD 6 Cyber Telco Retail M&amp;E</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>Progressive Corporation</t>
+          <t>Dollar General Corp.</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
         <is>
-          <t>progressive.com</t>
+          <t>dollargeneral.com</t>
         </is>
       </c>
       <c r="F109" s="5" t="inlineStr">
@@ -8803,11 +8769,11 @@
       </c>
       <c r="P109" s="5" t="inlineStr">
         <is>
-          <t>Auto Insurance</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n">
-        <v>75342</v>
+        <v>40612</v>
       </c>
       <c r="R109" s="5" t="inlineStr">
         <is>
@@ -8831,17 +8797,17 @@
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>POD 4 Banking Payments Insurance</t>
+          <t>POD 6 Cyber Telco Retail M&amp;E</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>U.S. Bancorp</t>
+          <t>Dollar Tree Inc.</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>usbank.com</t>
+          <t>dollartree.com</t>
         </is>
       </c>
       <c r="F110" s="5" t="inlineStr">
@@ -8878,11 +8844,11 @@
       </c>
       <c r="P110" s="5" t="inlineStr">
         <is>
-          <t>Regional Bank</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n">
-        <v>40496</v>
+        <v>30603</v>
       </c>
       <c r="R110" s="5" t="inlineStr">
         <is>
@@ -8906,17 +8872,17 @@
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>POD 4 Banking Payments Insurance</t>
+          <t>POD 6 Cyber Telco Retail M&amp;E</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Company</t>
+          <t>Home Depot Inc.</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
         <is>
-          <t>wellsfargo.com</t>
+          <t>homedepot.com</t>
         </is>
       </c>
       <c r="F111" s="5" t="inlineStr">
@@ -8953,11 +8919,11 @@
       </c>
       <c r="P111" s="5" t="inlineStr">
         <is>
-          <t>Money Center Bank</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n">
-        <v>82596</v>
+        <v>159514</v>
       </c>
       <c r="R111" s="5" t="inlineStr">
         <is>
@@ -8981,17 +8947,17 @@
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>POD 5 Consumer Internet Software Auto</t>
+          <t>POD 6 Cyber Telco Retail M&amp;E</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
+          <t>Kroger Co.</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
         <is>
-          <t>abc.xyz</t>
+          <t>kroger.com</t>
         </is>
       </c>
       <c r="F112" s="5" t="inlineStr">
@@ -9028,11 +8994,11 @@
       </c>
       <c r="P112" s="5" t="inlineStr">
         <is>
-          <t>Search / Cloud</t>
+          <t>Grocery</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n">
-        <v>350018</v>
+        <v>150039</v>
       </c>
       <c r="R112" s="5" t="inlineStr">
         <is>
@@ -9056,17 +9022,17 @@
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>POD 5 Consumer Internet Software Auto</t>
+          <t>POD 6 Cyber Telco Retail M&amp;E</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>Broadcom Inc.</t>
+          <t>Lowe's Companies</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
         <is>
-          <t>broadcom.com</t>
+          <t>lowes.com</t>
         </is>
       </c>
       <c r="F113" s="5" t="inlineStr">
@@ -9103,11 +9069,11 @@
       </c>
       <c r="P113" s="5" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n">
-        <v>51574</v>
+        <v>86377</v>
       </c>
       <c r="R113" s="5" t="inlineStr">
         <is>
@@ -9131,17 +9097,17 @@
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>POD 5 Consumer Internet Software Auto</t>
+          <t>POD 6 Cyber Telco Retail M&amp;E</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>General Motors Company</t>
+          <t>Performance Food Group</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>gm.com</t>
+          <t>pfgc.com</t>
         </is>
       </c>
       <c r="F114" s="5" t="inlineStr">
@@ -9178,11 +9144,11 @@
       </c>
       <c r="P114" s="5" t="inlineStr">
         <is>
-          <t>Auto OEM</t>
+          <t>Food Distribution</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n">
-        <v>187442</v>
+        <v>58281</v>
       </c>
       <c r="R114" s="5" t="inlineStr">
         <is>
@@ -9211,12 +9177,12 @@
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc.</t>
+          <t>Sysco Corporation</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
         <is>
-          <t>att.com</t>
+          <t>sysco.com</t>
         </is>
       </c>
       <c r="F115" s="5" t="inlineStr">
@@ -9253,11 +9219,11 @@
       </c>
       <c r="P115" s="5" t="inlineStr">
         <is>
-          <t>Telco</t>
+          <t>Food Distribution</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n">
-        <v>122336</v>
+        <v>79767</v>
       </c>
       <c r="R115" s="5" t="inlineStr">
         <is>
@@ -9286,12 +9252,12 @@
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>Best Buy Co.</t>
+          <t>TJX Companies</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>bestbuy.com</t>
+          <t>tjx.com</t>
         </is>
       </c>
       <c r="F116" s="5" t="inlineStr">
@@ -9332,7 +9298,7 @@
         </is>
       </c>
       <c r="Q116" s="4" t="n">
-        <v>41528</v>
+        <v>56360</v>
       </c>
       <c r="R116" s="5" t="inlineStr">
         <is>
@@ -9361,12 +9327,12 @@
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>Charter Communications</t>
+          <t>US Foods Holding</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
         <is>
-          <t>corporate.charter.com</t>
+          <t>usfoods.com</t>
         </is>
       </c>
       <c r="F117" s="5" t="inlineStr">
@@ -9403,11 +9369,11 @@
       </c>
       <c r="P117" s="5" t="inlineStr">
         <is>
-          <t>Cable</t>
+          <t>Food Distribution</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n">
-        <v>55085</v>
+        <v>37874</v>
       </c>
       <c r="R117" s="5" t="inlineStr">
         <is>
@@ -9436,12 +9402,12 @@
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>Costco Wholesale</t>
+          <t>Walgreens Boots Alliance</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>costco.com</t>
+          <t>walgreensbootsalliance.com</t>
         </is>
       </c>
       <c r="F118" s="5" t="inlineStr">
@@ -9478,11 +9444,11 @@
       </c>
       <c r="P118" s="5" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Pharmacy Retail</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n">
-        <v>254453</v>
+        <v>147658</v>
       </c>
       <c r="R118" s="5" t="inlineStr">
         <is>
@@ -9511,12 +9477,12 @@
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>Dollar General Corp.</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
         <is>
-          <t>dollargeneral.com</t>
+          <t>wbd.com</t>
         </is>
       </c>
       <c r="F119" s="5" t="inlineStr">
@@ -9553,11 +9519,11 @@
       </c>
       <c r="P119" s="5" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n">
-        <v>40612</v>
+        <v>39321</v>
       </c>
       <c r="R119" s="5" t="inlineStr">
         <is>
@@ -9581,17 +9547,17 @@
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>POD 6 Cyber Telco Retail M&amp;E</t>
+          <t>POD 7 Higher Education</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>Dollar Tree Inc.</t>
+          <t>Harvard University</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>dollartree.com</t>
+          <t>harvard.edu</t>
         </is>
       </c>
       <c r="F120" s="5" t="inlineStr">
@@ -9628,11 +9594,11 @@
       </c>
       <c r="P120" s="5" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Ivy League / R1</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n">
-        <v>30603</v>
+        <v>1320</v>
       </c>
       <c r="R120" s="5" t="inlineStr">
         <is>
@@ -9656,17 +9622,17 @@
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>POD 6 Cyber Telco Retail M&amp;E</t>
+          <t>POD 7 Higher Education</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>Home Depot Inc.</t>
+          <t>Ohio State University</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
         <is>
-          <t>homedepot.com</t>
+          <t>osu.edu</t>
         </is>
       </c>
       <c r="F121" s="5" t="inlineStr">
@@ -9703,11 +9669,11 @@
       </c>
       <c r="P121" s="5" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>R1 Research University</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n">
-        <v>159514</v>
+        <v>1370</v>
       </c>
       <c r="R121" s="5" t="inlineStr">
         <is>
@@ -9731,17 +9697,17 @@
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>POD 6 Cyber Telco Retail M&amp;E</t>
+          <t>POD 7 Higher Education</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>Kroger Co.</t>
+          <t>Pennsylvania State University</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>kroger.com</t>
+          <t>psu.edu</t>
         </is>
       </c>
       <c r="F122" s="5" t="inlineStr">
@@ -9778,11 +9744,11 @@
       </c>
       <c r="P122" s="5" t="inlineStr">
         <is>
-          <t>Grocery</t>
+          <t>R1 Research University</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n">
-        <v>150039</v>
+        <v>1239</v>
       </c>
       <c r="R122" s="5" t="inlineStr">
         <is>
@@ -9806,17 +9772,17 @@
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>POD 6 Cyber Telco Retail M&amp;E</t>
+          <t>POD 7 Higher Education</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>Lowe's Companies</t>
+          <t>University of California Los Angeles</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
         <is>
-          <t>lowes.com</t>
+          <t>ucla.edu</t>
         </is>
       </c>
       <c r="F123" s="5" t="inlineStr">
@@ -9853,11 +9819,11 @@
       </c>
       <c r="P123" s="5" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>R1 Research University</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n">
-        <v>86377</v>
+        <v>1623</v>
       </c>
       <c r="R123" s="5" t="inlineStr">
         <is>
@@ -9881,17 +9847,17 @@
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>POD 6 Cyber Telco Retail M&amp;E</t>
+          <t>POD 7 Higher Education</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>Performance Food Group</t>
+          <t>University of California San Diego</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>pfgc.com</t>
+          <t>ucsd.edu</t>
         </is>
       </c>
       <c r="F124" s="5" t="inlineStr">
@@ -9928,11 +9894,11 @@
       </c>
       <c r="P124" s="5" t="inlineStr">
         <is>
-          <t>Food Distribution</t>
+          <t>R1 Research University</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n">
-        <v>58281</v>
+        <v>1614</v>
       </c>
       <c r="R124" s="5" t="inlineStr">
         <is>
@@ -9956,17 +9922,17 @@
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>POD 6 Cyber Telco Retail M&amp;E</t>
+          <t>POD 7 Higher Education</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>Sysco Corporation</t>
+          <t>University of California San Francisco</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
         <is>
-          <t>sysco.com</t>
+          <t>ucsf.edu</t>
         </is>
       </c>
       <c r="F125" s="5" t="inlineStr">
@@ -10003,11 +9969,11 @@
       </c>
       <c r="P125" s="5" t="inlineStr">
         <is>
-          <t>Food Distribution</t>
+          <t>Medical Research University</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n">
-        <v>79767</v>
+        <v>1944</v>
       </c>
       <c r="R125" s="5" t="inlineStr">
         <is>
@@ -10031,17 +9997,17 @@
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>POD 6 Cyber Telco Retail M&amp;E</t>
+          <t>POD 7 Higher Education</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>TJX Companies</t>
+          <t>University of Maryland</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>tjx.com</t>
+          <t>umd.edu</t>
         </is>
       </c>
       <c r="F126" s="5" t="inlineStr">
@@ -10078,11 +10044,11 @@
       </c>
       <c r="P126" s="5" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>R1 Research University</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n">
-        <v>56360</v>
+        <v>1450</v>
       </c>
       <c r="R126" s="5" t="inlineStr">
         <is>
@@ -10106,17 +10072,17 @@
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>POD 6 Cyber Telco Retail M&amp;E</t>
+          <t>POD 7 Higher Education</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>US Foods Holding</t>
+          <t>University of Michigan</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>usfoods.com</t>
+          <t>umich.edu</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
@@ -10153,11 +10119,11 @@
       </c>
       <c r="P127" s="5" t="inlineStr">
         <is>
-          <t>Food Distribution</t>
+          <t>R1 Research University</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n">
-        <v>37874</v>
+        <v>1860</v>
       </c>
       <c r="R127" s="5" t="inlineStr">
         <is>
@@ -10181,17 +10147,17 @@
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>POD 6 Cyber Telco Retail M&amp;E</t>
+          <t>POD 7 Higher Education</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>Walgreens Boots Alliance</t>
+          <t>University of North Carolina</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
         <is>
-          <t>walgreensbootsalliance.com</t>
+          <t>unc.edu</t>
         </is>
       </c>
       <c r="F128" s="5" t="inlineStr">
@@ -10228,11 +10194,11 @@
       </c>
       <c r="P128" s="5" t="inlineStr">
         <is>
-          <t>Pharmacy Retail</t>
+          <t>R1 Research University</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n">
-        <v>147658</v>
+        <v>1300</v>
       </c>
       <c r="R128" s="5" t="inlineStr">
         <is>
@@ -10256,17 +10222,17 @@
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>POD 6 Cyber Telco Retail M&amp;E</t>
+          <t>POD 7 Higher Education</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>University of Pennsylvania</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
         <is>
-          <t>wbd.com</t>
+          <t>upenn.edu</t>
         </is>
       </c>
       <c r="F129" s="5" t="inlineStr">
@@ -10303,11 +10269,11 @@
       </c>
       <c r="P129" s="5" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Ivy League / R1</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n">
-        <v>39321</v>
+        <v>1696</v>
       </c>
       <c r="R129" s="5" t="inlineStr">
         <is>
@@ -10336,12 +10302,12 @@
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>Harvard University</t>
+          <t>University of Washington</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
         <is>
-          <t>harvard.edu</t>
+          <t>washington.edu</t>
         </is>
       </c>
       <c r="F130" s="5" t="inlineStr">
@@ -10378,11 +10344,11 @@
       </c>
       <c r="P130" s="5" t="inlineStr">
         <is>
-          <t>Ivy League / R1</t>
+          <t>R1 Research University</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n">
-        <v>1320</v>
+        <v>1672</v>
       </c>
       <c r="R130" s="5" t="inlineStr">
         <is>
@@ -10411,12 +10377,12 @@
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>Ohio State University</t>
+          <t>University of Wisconsin-Madison</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
         <is>
-          <t>osu.edu</t>
+          <t>wisc.edu</t>
         </is>
       </c>
       <c r="F131" s="5" t="inlineStr">
@@ -10457,7 +10423,7 @@
         </is>
       </c>
       <c r="Q131" s="4" t="n">
-        <v>1370</v>
+        <v>1620</v>
       </c>
       <c r="R131" s="5" t="inlineStr">
         <is>
@@ -10481,17 +10447,17 @@
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>POD 7 Higher Education</t>
+          <t>POD 4 Banking Payments Insurance</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>Pennsylvania State University</t>
+          <t>Travelers Companies</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>psu.edu</t>
+          <t>travelers.com</t>
         </is>
       </c>
       <c r="F132" s="5" t="inlineStr">
@@ -10500,11 +10466,11 @@
         </is>
       </c>
       <c r="G132" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H132" s="4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-100.0%</t>
         </is>
       </c>
       <c r="I132" s="5" t="inlineStr">
@@ -10516,7 +10482,7 @@
         <v>0</v>
       </c>
       <c r="K132" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L132" s="4" t="inlineStr"/>
       <c r="M132" s="4" t="inlineStr"/>
@@ -10528,11 +10494,11 @@
       </c>
       <c r="P132" s="5" t="inlineStr">
         <is>
-          <t>R1 Research University</t>
+          <t>P&amp;C Insurance</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n">
-        <v>1239</v>
+        <v>46421</v>
       </c>
       <c r="R132" s="5" t="inlineStr">
         <is>
@@ -10556,17 +10522,17 @@
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>POD 7 Higher Education</t>
+          <t>POD 5 Consumer Internet Software Auto</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>University of California Los Angeles</t>
+          <t>Comcast Corporation</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>ucla.edu</t>
+          <t>corporate.comcast.com</t>
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr">
@@ -10575,11 +10541,11 @@
         </is>
       </c>
       <c r="G133" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H133" s="4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-100.0%</t>
         </is>
       </c>
       <c r="I133" s="5" t="inlineStr">
@@ -10591,7 +10557,7 @@
         <v>0</v>
       </c>
       <c r="K133" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L133" s="4" t="inlineStr"/>
       <c r="M133" s="4" t="inlineStr"/>
@@ -10603,11 +10569,11 @@
       </c>
       <c r="P133" s="5" t="inlineStr">
         <is>
-          <t>R1 Research University</t>
+          <t>Cable / Media</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n">
-        <v>1623</v>
+        <v>123731</v>
       </c>
       <c r="R133" s="5" t="inlineStr">
         <is>
@@ -10631,17 +10597,17 @@
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>POD 7 Higher Education</t>
+          <t>POD 5 Consumer Internet Software Auto</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>University of California San Diego</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>ucsd.edu</t>
+          <t>stellantis.com</t>
         </is>
       </c>
       <c r="F134" s="5" t="inlineStr">
@@ -10650,11 +10616,11 @@
         </is>
       </c>
       <c r="G134" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H134" s="4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-100.0%</t>
         </is>
       </c>
       <c r="I134" s="5" t="inlineStr">
@@ -10666,7 +10632,7 @@
         <v>0</v>
       </c>
       <c r="K134" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L134" s="4" t="inlineStr"/>
       <c r="M134" s="4" t="inlineStr"/>
@@ -10678,11 +10644,11 @@
       </c>
       <c r="P134" s="5" t="inlineStr">
         <is>
-          <t>R1 Research University</t>
+          <t>Auto OEM</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n">
-        <v>1614</v>
+        <v>201202</v>
       </c>
       <c r="R134" s="5" t="inlineStr">
         <is>
@@ -10706,17 +10672,17 @@
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>POD 7 Higher Education</t>
+          <t>POD 5 Consumer Internet Software Auto</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>University of California San Francisco</t>
+          <t>Cisco Systems Inc.</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
         <is>
-          <t>ucsf.edu</t>
+          <t>cisco.com</t>
         </is>
       </c>
       <c r="F135" s="5" t="inlineStr">
@@ -10725,11 +10691,11 @@
         </is>
       </c>
       <c r="G135" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H135" s="4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-100.0%</t>
         </is>
       </c>
       <c r="I135" s="5" t="inlineStr">
@@ -10741,7 +10707,7 @@
         <v>0</v>
       </c>
       <c r="K135" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L135" s="4" t="inlineStr"/>
       <c r="M135" s="4" t="inlineStr"/>
@@ -10753,11 +10719,11 @@
       </c>
       <c r="P135" s="5" t="inlineStr">
         <is>
-          <t>Medical Research University</t>
+          <t>Networking</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n">
-        <v>1944</v>
+        <v>53803</v>
       </c>
       <c r="R135" s="5" t="inlineStr">
         <is>
@@ -10781,17 +10747,17 @@
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>POD 7 Higher Education</t>
+          <t>POD 5 Consumer Internet Software Auto</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>University of Maryland</t>
+          <t>Salesforce Inc.</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>umd.edu</t>
+          <t>salesforce.com</t>
         </is>
       </c>
       <c r="F136" s="5" t="inlineStr">
@@ -10800,11 +10766,11 @@
         </is>
       </c>
       <c r="G136" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="H136" s="4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-100.0%</t>
         </is>
       </c>
       <c r="I136" s="5" t="inlineStr">
@@ -10816,7 +10782,7 @@
         <v>0</v>
       </c>
       <c r="K136" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L136" s="4" t="inlineStr"/>
       <c r="M136" s="4" t="inlineStr"/>
@@ -10828,11 +10794,11 @@
       </c>
       <c r="P136" s="5" t="inlineStr">
         <is>
-          <t>R1 Research University</t>
+          <t>SaaS</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n">
-        <v>1450</v>
+        <v>37895</v>
       </c>
       <c r="R136" s="5" t="inlineStr">
         <is>
@@ -10856,17 +10822,17 @@
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>POD 7 Higher Education</t>
+          <t>POD 5 Consumer Internet Software Auto</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>University of Michigan</t>
+          <t>Netflix Inc.</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
         <is>
-          <t>umich.edu</t>
+          <t>netflix.com</t>
         </is>
       </c>
       <c r="F137" s="5" t="inlineStr">
@@ -10875,11 +10841,11 @@
         </is>
       </c>
       <c r="G137" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="H137" s="4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-100.0%</t>
         </is>
       </c>
       <c r="I137" s="5" t="inlineStr">
@@ -10891,7 +10857,7 @@
         <v>0</v>
       </c>
       <c r="K137" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L137" s="4" t="inlineStr"/>
       <c r="M137" s="4" t="inlineStr"/>
@@ -10903,11 +10869,11 @@
       </c>
       <c r="P137" s="5" t="inlineStr">
         <is>
-          <t>R1 Research University</t>
+          <t>Streaming</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n">
-        <v>1860</v>
+        <v>39001</v>
       </c>
       <c r="R137" s="5" t="inlineStr">
         <is>
@@ -10931,17 +10897,17 @@
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>POD 7 Higher Education</t>
+          <t>POD 4 Banking Payments Insurance</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>University of North Carolina</t>
+          <t>Mastercard Incorporated</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
         <is>
-          <t>unc.edu</t>
+          <t>mastercard.com</t>
         </is>
       </c>
       <c r="F138" s="5" t="inlineStr">
@@ -10950,11 +10916,11 @@
         </is>
       </c>
       <c r="G138" s="4" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="H138" s="4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-100.0%</t>
         </is>
       </c>
       <c r="I138" s="5" t="inlineStr">
@@ -10966,7 +10932,7 @@
         <v>0</v>
       </c>
       <c r="K138" s="5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L138" s="4" t="inlineStr"/>
       <c r="M138" s="4" t="inlineStr"/>
@@ -10978,11 +10944,11 @@
       </c>
       <c r="P138" s="5" t="inlineStr">
         <is>
-          <t>R1 Research University</t>
+          <t>Payment Networks</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n">
-        <v>1300</v>
+        <v>28167</v>
       </c>
       <c r="R138" s="5" t="inlineStr">
         <is>
@@ -11006,17 +10972,17 @@
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>POD 7 Higher Education</t>
+          <t>POD 4 Banking Payments Insurance</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>University of Pennsylvania</t>
+          <t>Citigroup Inc.</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
         <is>
-          <t>upenn.edu</t>
+          <t>citigroup.com</t>
         </is>
       </c>
       <c r="F139" s="5" t="inlineStr">
@@ -11025,11 +10991,11 @@
         </is>
       </c>
       <c r="G139" s="4" t="n">
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="H139" s="4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-100.0%</t>
         </is>
       </c>
       <c r="I139" s="5" t="inlineStr">
@@ -11041,7 +11007,7 @@
         <v>0</v>
       </c>
       <c r="K139" s="5" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L139" s="4" t="inlineStr"/>
       <c r="M139" s="4" t="inlineStr"/>
@@ -11053,11 +11019,11 @@
       </c>
       <c r="P139" s="5" t="inlineStr">
         <is>
-          <t>Ivy League / R1</t>
+          <t>Money Center Bank</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n">
-        <v>1696</v>
+        <v>71355</v>
       </c>
       <c r="R139" s="5" t="inlineStr">
         <is>
@@ -11081,17 +11047,17 @@
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>POD 7 Higher Education</t>
+          <t>POD 5 Consumer Internet Software Auto</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>University of Washington</t>
+          <t>Tesla Inc.</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>washington.edu</t>
+          <t>tesla.com</t>
         </is>
       </c>
       <c r="F140" s="5" t="inlineStr">
@@ -11100,11 +11066,11 @@
         </is>
       </c>
       <c r="G140" s="4" t="n">
-        <v>0</v>
+        <v>-21</v>
       </c>
       <c r="H140" s="4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-100.0%</t>
         </is>
       </c>
       <c r="I140" s="5" t="inlineStr">
@@ -11116,7 +11082,7 @@
         <v>0</v>
       </c>
       <c r="K140" s="5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="L140" s="4" t="inlineStr"/>
       <c r="M140" s="4" t="inlineStr"/>
@@ -11128,11 +11094,11 @@
       </c>
       <c r="P140" s="5" t="inlineStr">
         <is>
-          <t>R1 Research University</t>
+          <t>EV / Auto</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n">
-        <v>1672</v>
+        <v>97690</v>
       </c>
       <c r="R140" s="5" t="inlineStr">
         <is>
@@ -11156,17 +11122,17 @@
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>POD 7 Higher Education</t>
+          <t>POD 5 Consumer Internet Software Auto</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>University of Wisconsin-Madison</t>
+          <t>Qualcomm Inc.</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
         <is>
-          <t>wisc.edu</t>
+          <t>qualcomm.com</t>
         </is>
       </c>
       <c r="F141" s="5" t="inlineStr">
@@ -11175,11 +11141,11 @@
         </is>
       </c>
       <c r="G141" s="4" t="n">
-        <v>0</v>
+        <v>-29</v>
       </c>
       <c r="H141" s="4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-100.0%</t>
         </is>
       </c>
       <c r="I141" s="5" t="inlineStr">
@@ -11191,7 +11157,7 @@
         <v>0</v>
       </c>
       <c r="K141" s="5" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="L141" s="4" t="inlineStr"/>
       <c r="M141" s="4" t="inlineStr"/>
@@ -11203,11 +11169,11 @@
       </c>
       <c r="P141" s="5" t="inlineStr">
         <is>
-          <t>R1 Research University</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n">
-        <v>1620</v>
+        <v>38962</v>
       </c>
       <c r="R141" s="5" t="inlineStr">
         <is>
